--- a/tame_output/ON/bt/strategyON_20240514.xlsx
+++ b/tame_output/ON/bt/strategyON_20240514.xlsx
@@ -46700,10 +46700,10 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.155669783113987</v>
+        <v>-4.155600332515977</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.202985564621532</v>
+        <v>1.203013344860736</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3349554519816608</v>

--- a/tame_output/ON/bt/strategyON_20240514.xlsx
+++ b/tame_output/ON/bt/strategyON_20240514.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.0%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>112.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.4%</t>
+          <t>444.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-577.1%</t>
+          <t>-586.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-255.9%</t>
+          <t>-259.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-246.8%</t>
+          <t>-172.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-257.5%</t>
+          <t>-267.4%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,17 +1476,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-179.6%</t>
+          <t>-185.5%</t>
         </is>
       </c>
     </row>
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.914589657731931</v>
+        <v>-4.014186568025008</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.16338238382869</v>
+        <v>1.123543619711459</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.07514137070643517</v>
+        <v>-0.02445553958664204</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.774659493659071</v>
+        <v>2.714901347483224</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.802212656549258</v>
+        <v>-3.901809566842335</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.213824480132426</v>
+        <v>1.173985716015195</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.07514137070643517</v>
+        <v>-0.02445553958664204</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.780150789489738</v>
+        <v>2.720392643313891</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.000447225435988</v>
+        <v>-4.100044135729066</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.146027854346273</v>
+        <v>1.106189090229042</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1230931981802954</v>
+        <v>-0.2226901084733726</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.672707249926238</v>
+        <v>2.612949103750392</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.083448506461267</v>
+        <v>-4.183045416754345</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9511830619368145</v>
+        <v>0.9113442978195836</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1416640827074692</v>
+        <v>-0.2412609930005464</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.499920439210587</v>
+        <v>2.440162293034741</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.924254234404691</v>
+        <v>-4.023851144697769</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.135010431478651</v>
+        <v>1.09517166736142</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1416640827074692</v>
+        <v>-0.2412609930005464</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.620070099929793</v>
+        <v>2.560311953753947</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.010852817385794</v>
+        <v>-4.110449727678872</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.114884024388532</v>
+        <v>1.075045260271301</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1416640827074692</v>
+        <v>-0.2412609930005464</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.634583126032116</v>
+        <v>2.57482497985627</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.972469154827643</v>
+        <v>-4.072066065120721</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.127656930754161</v>
+        <v>1.08781816663693</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.103280420149318</v>
+        <v>-0.2028773304423952</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.655032764909376</v>
+        <v>2.595274618733529</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.795352824792477</v>
+        <v>-3.894949735085555</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.19523249161353</v>
+        <v>1.155393727496299</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.103280420149318</v>
+        <v>-0.2028773304423952</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.651761793754678</v>
+        <v>2.592003647578831</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.765650700816184</v>
+        <v>-3.865247611109261</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.20779673296596</v>
+        <v>1.167957968848729</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1077505453646314</v>
+        <v>-0.2073474556577086</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.649763110387402</v>
+        <v>2.590004964211556</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.586275279577416</v>
+        <v>-3.685872189870493</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.273333876767882</v>
+        <v>1.233495112650651</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.04902621280608732</v>
+        <v>-0.05057069748698989</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.737616140596248</v>
+        <v>2.677857994420402</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.631289493098022</v>
+        <v>-3.7308864033911</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.236135646691229</v>
+        <v>1.196296882573998</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.01867731749148271</v>
+        <v>-0.0809195928015945</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.700214258739075</v>
+        <v>2.640456112563229</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.898294003370458</v>
+        <v>-3.997890913663535</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.135025404921201</v>
+        <v>1.09518664080397</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1756857205514659</v>
+        <v>-0.2752826308445431</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.589287998252252</v>
+        <v>2.529529852076405</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.187081223829373</v>
+        <v>-4.28667813412245</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.018714438634136</v>
+        <v>0.9788756745169049</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2767718406504662</v>
+        <v>-0.3763687509435434</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.527840248089353</v>
+        <v>2.468082101913506</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.154605637658601</v>
+        <v>-4.254202547951678</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.029304634656762</v>
+        <v>0.9894658705395305</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2767718406504662</v>
+        <v>-0.3763687509435434</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.52544020964367</v>
+        <v>2.465682063467823</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.135567509951303</v>
+        <v>-4.235164420244381</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.033444604947925</v>
+        <v>0.9936058408306945</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3349554519816608</v>
+        <v>-0.434552362274738</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.487054762053198</v>
+        <v>2.427296615877351</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.746975888609912</v>
+        <v>3.391742440841397</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.155600332515977</v>
+        <v>-4.251910285500756</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.203013344860736</v>
+        <v>1.164489363666825</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3349554519816608</v>
+        <v>-0.434552362274738</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.664636630991879</v>
+        <v>2.604878484816032</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240514.xlsx
+++ b/tame_output/ON/bt/strategyON_20240514.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.6%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>56.4%</t>
         </is>
       </c>
     </row>
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-77.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.9%</t>
+          <t>112.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.6%</t>
+          <t>131.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.7%</t>
+          <t>-52.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.1%</t>
+          <t>448.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-586.8%</t>
+          <t>-560.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,27 +1150,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.3%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-169.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-259.8%</t>
+          <t>-249.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>-464.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-172.4%</t>
+          <t>-182.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-267.4%</t>
+          <t>-247.6%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-185.5%</t>
+          <t>-173.6%</t>
         </is>
       </c>
     </row>
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.46121771111398</v>
+        <v>-11.29911483439</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.423089333308192</v>
+        <v>-1.358248182618599</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.034878346804777</v>
+        <v>-2.936139185152558</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.340827167368281</v>
+        <v>1.400070664359613</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.40920219714517</v>
+        <v>-11.24709932042119</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.398292792034266</v>
+        <v>-1.333451641344673</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.034878346804777</v>
+        <v>-2.936139185152558</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.344817503054682</v>
+        <v>1.404061000046014</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.55087403886929</v>
+        <v>-11.38877116214531</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.456436755622656</v>
+        <v>-1.391595604933062</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.034878346804777</v>
+        <v>-2.936139185152558</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.343342276155941</v>
+        <v>1.402585773147272</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.50128319444445</v>
+        <v>-11.33918031772047</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.42154700768785</v>
+        <v>-1.356705856998257</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.985287502379943</v>
+        <v>-2.886548340727725</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.388150192975713</v>
+        <v>1.447393689967045</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.30213108720736</v>
+        <v>-11.14002821048337</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.354937298439693</v>
+        <v>-1.2900961477501</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.81996497643013</v>
+        <v>-2.721225814777911</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.474292574898918</v>
+        <v>1.53353607189025</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.07628593448795</v>
+        <v>-10.91418305776396</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.255020164315721</v>
+        <v>-1.190179013626127</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.778038300842967</v>
+        <v>-2.679299139190748</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.509027653287425</v>
+        <v>1.568271150278756</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.95170727815035</v>
+        <v>-10.78960440142637</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.204049557224625</v>
+        <v>-1.139208406535031</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.778038300842967</v>
+        <v>-2.679299139190748</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.510166797843484</v>
+        <v>1.569410294834815</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.00460256619464</v>
+        <v>-10.84249968947065</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.222573898280232</v>
+        <v>-1.157732747590638</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.77308295475452</v>
+        <v>-2.674343793102302</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.515773779658659</v>
+        <v>1.575017276649991</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.72069383526589</v>
+        <v>-10.55859095854191</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.103276701670096</v>
+        <v>-1.038435550980502</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.77308295475452</v>
+        <v>-2.674343793102302</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.521507483897296</v>
+        <v>1.580750980888627</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.64932744265624</v>
+        <v>-10.48722456593226</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.084467407020102</v>
+        <v>-1.019626256330509</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.701716562144873</v>
+        <v>-2.602977400492654</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.554590057069219</v>
+        <v>1.613833554060551</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.38549057545217</v>
+        <v>-10.22338769872819</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9888161414513816</v>
+        <v>-0.923974990761788</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.701716562144873</v>
+        <v>-2.602977400492654</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.544706575756312</v>
+        <v>1.603950072747643</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.11824877458378</v>
+        <v>-9.956145897859791</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8837539816033968</v>
+        <v>-0.8189128309138027</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.701716562144873</v>
+        <v>-2.602977400492654</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.542872015256938</v>
+        <v>1.602115512248269</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.02034173590729</v>
+        <v>-9.858238859183301</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8448914811062616</v>
+        <v>-0.780050330416667</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.633730812284316</v>
+        <v>-2.534991650632097</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.583363150199811</v>
+        <v>1.642606647191142</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.996388194931328</v>
+        <v>-9.834285318207343</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8346415585703846</v>
+        <v>-0.7698004078807905</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.609777271308359</v>
+        <v>-2.51103810965614</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.598403780930879</v>
+        <v>1.65764727792221</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.732328256608531</v>
+        <v>-9.570225379884546</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7422778994030179</v>
+        <v>-0.6774367487134239</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.345717332985563</v>
+        <v>-2.246978171333344</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.743579427762805</v>
+        <v>1.802822924754136</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.025248633103693</v>
+        <v>-8.863145756379708</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4622330836613839</v>
+        <v>-0.3973919329717899</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.345717332985563</v>
+        <v>-2.246978171333344</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.740792394102504</v>
+        <v>1.800035891093835</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.985064334737503</v>
+        <v>-8.822961458013518</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4458157404270664</v>
+        <v>-0.3809745897374723</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.305533034619372</v>
+        <v>-2.206793872967153</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.765246597010059</v>
+        <v>1.824490094001391</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.904994539199699</v>
+        <v>-8.742891662475714</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4144210009911875</v>
+        <v>-0.3495798503015934</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.225463239081568</v>
+        <v>-2.126724077429349</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.812655295553499</v>
+        <v>1.87189879254483</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.671513316970099</v>
+        <v>-8.509410440246114</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3131040832614955</v>
+        <v>-0.2482629325719015</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.991982016851969</v>
+        <v>-1.89324285519975</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.960668457729111</v>
+        <v>2.019911954720442</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.521846925962585</v>
+        <v>-8.3597440492386</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2561297371714488</v>
+        <v>-0.1912885864818548</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.899078525609433</v>
+        <v>-1.800339363957215</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.013518342161673</v>
+        <v>2.072761839153004</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.389571452331698</v>
+        <v>-8.227468575607713</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2078520609720669</v>
+        <v>-0.1430109102824728</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.766803051978547</v>
+        <v>-1.668063890326328</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.088251113087232</v>
+        <v>2.147494610078563</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.198971777658544</v>
+        <v>-8.036868900934559</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1287971304151689</v>
+        <v>-0.06395597972557487</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.576203377305394</v>
+        <v>-1.477464215653175</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.20542597857876</v>
+        <v>2.264669475570091</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.949971978974963</v>
+        <v>-7.787869102250978</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.01629086971807769</v>
+        <v>0.04855028097151637</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.576203377305394</v>
+        <v>-1.477464215653175</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.218332319802419</v>
+        <v>2.27757581679375</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.055561968748068</v>
+        <v>-7.893459092024083</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1865027952265379</v>
+        <v>-0.1216616445369443</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.681793367078498</v>
+        <v>-1.583054205426279</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.027002396339338</v>
+        <v>2.086245893330669</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.074296870866664</v>
+        <v>-7.91219399414268</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1454524141968907</v>
+        <v>-0.08061126350729664</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.681793367078498</v>
+        <v>-1.583054205426279</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.075546738216424</v>
+        <v>2.134790235207755</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.926356829459065</v>
+        <v>-7.76425395273508</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2061553203220186</v>
+        <v>-0.1413141696324245</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.661472451169941</v>
+        <v>-1.562733289517722</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.967860365073391</v>
+        <v>2.027103862064722</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.902128193070093</v>
+        <v>-7.740025316346108</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2051778520199075</v>
+        <v>-0.1403367013303134</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.637243814780968</v>
+        <v>-1.538504653128749</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.973683560653296</v>
+        <v>2.032927057644628</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.858579786299402</v>
+        <v>-7.696476909575417</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1947191014067244</v>
+        <v>-0.1298779507171304</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.637243814780968</v>
+        <v>-1.538504653128749</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.966722948558203</v>
+        <v>2.025966445549535</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.616431392845544</v>
+        <v>-7.454328516121559</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.08339738964403809</v>
+        <v>-0.01855623895444403</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.637243814780968</v>
+        <v>-1.538504653128749</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.981185302939346</v>
+        <v>2.040428799930678</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.553202021077196</v>
+        <v>-7.391099144353211</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.06357352047750364</v>
+        <v>0.001267630212089976</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.637243814780968</v>
+        <v>-1.538504653128749</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.975717423398541</v>
+        <v>2.034960920389873</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.429910886260065</v>
+        <v>-7.26780800953608</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.01675897254007452</v>
+        <v>0.04808217814951954</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.513952679963838</v>
+        <v>-1.415213518311619</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.047190198299396</v>
+        <v>2.106433695290728</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.408761687356622</v>
+        <v>-7.246658810632637</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.0005983147413721746</v>
+        <v>0.06424283594822189</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.492803481060395</v>
+        <v>-1.394064319408176</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.067580695878787</v>
+        <v>2.126824192870119</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.164996245373177</v>
+        <v>-7.002893368649192</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.09268857039905631</v>
+        <v>0.1575297210886504</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.492803481060395</v>
+        <v>-1.394064319408176</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.063361404225838</v>
+        <v>2.122604901217169</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.900968178179918</v>
+        <v>-6.738865301455933</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.200424111196376</v>
+        <v>0.2652652618859701</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.290938082244441</v>
+        <v>-1.192198920592222</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.186604957435426</v>
+        <v>2.245848454426758</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.651117784230843</v>
+        <v>-6.489014907506858</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2931063437597081</v>
+        <v>0.3579474944493022</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.290938082244441</v>
+        <v>-1.192198920592222</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.179347032419129</v>
+        <v>2.23859052941046</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.475225691763411</v>
+        <v>-6.313122815039426</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3670623042673298</v>
+        <v>0.4319034549569238</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.290938082244441</v>
+        <v>-1.192198920592222</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.182946155939777</v>
+        <v>2.242189652931109</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.303779228740948</v>
+        <v>-6.141676352016963</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4489683955308688</v>
+        <v>0.5138095462204628</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.119491619221978</v>
+        <v>-1.020752457569759</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.299141539807809</v>
+        <v>2.35838503679914</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.078746229072125</v>
+        <v>-5.91664335234814</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5380020730146948</v>
+        <v>0.6028432237042889</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8944586195531549</v>
+        <v>-0.795719457900936</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.4331818172254</v>
+        <v>2.492425314216731</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.864111851435718</v>
+        <v>-5.702008974711733</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6285506251235748</v>
+        <v>0.6933917758131689</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6798242419167481</v>
+        <v>-0.5810850802645292</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.566657244861561</v>
+        <v>2.625900741852892</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.77111181022982</v>
+        <v>-5.609008933505835</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6469449003897298</v>
+        <v>0.7117860510793239</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6798242419167481</v>
+        <v>-0.5810850802645292</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.547851503645357</v>
+        <v>2.607095000636688</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.530681313424959</v>
+        <v>-5.368578436700974</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7448601757365516</v>
+        <v>0.8097013264261452</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4393937451118878</v>
+        <v>-0.3406545834596689</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.69385287835315</v>
+        <v>2.753096375344481</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.458438745253765</v>
+        <v>-5.29633586852978</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7776865168398497</v>
+        <v>0.8425276675294433</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4393937451118878</v>
+        <v>-0.3406545834596689</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.69778219218797</v>
+        <v>2.757025689179302</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.342498895628579</v>
+        <v>-5.180396018904594</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8247410406072637</v>
+        <v>0.8895821912968578</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3625720140957639</v>
+        <v>-0.263832852443545</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.744553814714985</v>
+        <v>2.803797311706316</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.099843307205417</v>
+        <v>-4.937740430481432</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9188013471965224</v>
+        <v>0.9836424978861162</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3625720140957639</v>
+        <v>-0.263832852443545</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.741551885934978</v>
+        <v>2.800795382926309</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.879822509168406</v>
+        <v>-4.717719632444421</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.008388703421941</v>
+        <v>1.073229854111535</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2213521690277837</v>
+        <v>-0.1226130073755648</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.82786282998638</v>
+        <v>2.887106326977712</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.746954820105128</v>
+        <v>-4.584851943381143</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.077429961849075</v>
+        <v>1.142271112538669</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2213521690277837</v>
+        <v>-0.1226130073755648</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.843757012788203</v>
+        <v>2.903000509779535</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.587439716585759</v>
+        <v>-4.425336839861774</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.142381847697125</v>
+        <v>1.207222998386719</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.06183706550841372</v>
+        <v>0.03690209614380513</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.940611919340127</v>
+        <v>2.999855416331459</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.442767571486021</v>
+        <v>-4.280664694762036</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.21033880829846</v>
+        <v>1.275179958988053</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.08283507959132369</v>
+        <v>0.1815742412435425</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.03750330896141</v>
+        <v>3.096746805952741</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.502642398843713</v>
+        <v>-4.340539522119728</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.172426368756808</v>
+        <v>1.237267519446402</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.02296025223363157</v>
+        <v>0.1216994138858504</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.98761590394822</v>
+        <v>3.046859400939552</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.415842901064705</v>
+        <v>-4.25374002434072</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.229546661190978</v>
+        <v>1.294387811880572</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.02296025223363157</v>
+        <v>0.1216994138858504</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.010016397270786</v>
+        <v>3.069259894262118</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.418312607526511</v>
+        <v>-4.256209730802526</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.228631179979668</v>
+        <v>1.293472330669262</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.02049054577182541</v>
+        <v>0.1192297074240443</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.008606974767115</v>
+        <v>3.067850471758446</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.486682793850521</v>
+        <v>-4.324579917126536</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.212290027924765</v>
+        <v>1.27713117861436</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.1285054064602592</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.025179316663546</v>
+        <v>3.084422813654877</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.365266364224045</v>
+        <v>-4.20316348750006</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.251293308407248</v>
+        <v>1.316134459096841</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.1285054064602592</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.015616025295437</v>
+        <v>3.074859522286769</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.39625952355275</v>
+        <v>-4.234156646828765</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.063605609716152</v>
+        <v>1.128446760405746</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.1285054064602592</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.840325590335824</v>
+        <v>2.899569087327155</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.220785263760281</v>
+        <v>-4.058682387036296</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.138362545624928</v>
+        <v>1.203203696314522</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.1285054064602592</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.844892822327612</v>
+        <v>2.904136319318943</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.331721516401529</v>
+        <v>-4.169618639677545</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.069730073329635</v>
+        <v>1.134571224019229</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.1285054064602592</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.820634851088819</v>
+        <v>2.87987834808015</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.534748093944763</v>
+        <v>-4.372645217220778</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9916508275322475</v>
+        <v>1.056491978221842</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.173260332735193</v>
+        <v>-0.07452117108297418</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.701950289782785</v>
+        <v>2.761193786774116</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.37682249500947</v>
+        <v>-4.214719618285485</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.064993453538497</v>
+        <v>1.129834604228091</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.173260332735193</v>
+        <v>-0.07452117108297418</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.712122676214917</v>
+        <v>2.771366173206248</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.290579031983092</v>
+        <v>-4.128476155259107</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.094437109322909</v>
+        <v>1.159278260012502</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.173260332735193</v>
+        <v>-0.07452117108297418</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.707068946788777</v>
+        <v>2.766312443780108</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.291762116634153</v>
+        <v>-4.129659239910168</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.085739650907009</v>
+        <v>1.150580801596603</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1789033812017046</v>
+        <v>-0.08016421954948572</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.695458893153396</v>
+        <v>2.754702390144727</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.16863440964007</v>
+        <v>-4.006531532916085</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.135542606737744</v>
+        <v>1.200383757427338</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1789033812017046</v>
+        <v>-0.08016421954948572</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.696010766186497</v>
+        <v>2.755254263177828</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.075823928189211</v>
+        <v>-3.913721051465226</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.101939491209454</v>
+        <v>1.166780641899048</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.08609289975084522</v>
+        <v>0.01264626190137363</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.680969746948378</v>
+        <v>2.74021324393971</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.027260875968181</v>
+        <v>-3.865157999244196</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.123238188022467</v>
+        <v>1.188079338712061</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.03752984752981503</v>
+        <v>0.06120931412240382</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.711981054205598</v>
+        <v>2.771224551196929</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.014186568025008</v>
+        <v>-3.752486781007946</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.123543619711459</v>
+        <v>1.228223534518284</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.02445553958664204</v>
+        <v>0.173880532358654</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.714901347483224</v>
+        <v>2.833902990650402</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.901809566842335</v>
+        <v>-3.640109779825273</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.173985716015195</v>
+        <v>1.27866563082202</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.02445553958664204</v>
+        <v>0.173880532358654</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.720392643313891</v>
+        <v>2.839394286481069</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.100044135729066</v>
+        <v>-3.838344348712003</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.106189090229042</v>
+        <v>1.210869005035867</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2226901084733726</v>
+        <v>-0.02435403652807655</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.612949103750392</v>
+        <v>2.73195074691757</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.183045416754345</v>
+        <v>-3.921345629737282</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9113442978195836</v>
+        <v>1.016024212626409</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2412609930005464</v>
+        <v>-0.04292492105525031</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.440162293034741</v>
+        <v>2.559163936201919</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.023851144697769</v>
+        <v>-3.762151357680706</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.09517166736142</v>
+        <v>1.199851582168245</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2412609930005464</v>
+        <v>-0.04292492105525031</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.560311953753947</v>
+        <v>2.679313596921125</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.110449727678872</v>
+        <v>-3.848749940661809</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.075045260271301</v>
+        <v>1.179725175078126</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2412609930005464</v>
+        <v>-0.04292492105525031</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.57482497985627</v>
+        <v>2.693826623023448</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.072066065120721</v>
+        <v>-3.810366278103658</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.08781816663693</v>
+        <v>1.192498081443756</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2028773304423952</v>
+        <v>-0.004541258497099132</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.595274618733529</v>
+        <v>2.714276261900707</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.894949735085555</v>
+        <v>-3.633249948068492</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.155393727496299</v>
+        <v>1.260073642303124</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2028773304423952</v>
+        <v>-0.004541258497099132</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.592003647578831</v>
+        <v>2.711005290746009</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.865247611109261</v>
+        <v>-3.603547824092198</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.167957968848729</v>
+        <v>1.272637883655555</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2073474556577086</v>
+        <v>-0.009011383712412502</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.590004964211556</v>
+        <v>2.709006607378734</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.685872189870493</v>
+        <v>-3.42417240285343</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.233495112650651</v>
+        <v>1.338175027457476</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.05057069748698989</v>
+        <v>0.1477653744583062</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.677857994420402</v>
+        <v>2.796859637587579</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.7308864033911</v>
+        <v>-3.469186616374036</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.196296882573998</v>
+        <v>1.300976797380823</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.0809195928015945</v>
+        <v>0.1174164791437016</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.640456112563229</v>
+        <v>2.759457755730407</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.997890913663535</v>
+        <v>-3.736191126646472</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.09518664080397</v>
+        <v>1.199866555610795</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2752826308445431</v>
+        <v>-0.07694655889924701</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.529529852076405</v>
+        <v>2.648531495243583</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.28667813412245</v>
+        <v>-4.024978347105387</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9788756745169049</v>
+        <v>1.08355558932373</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3763687509435434</v>
+        <v>-0.1780326789982474</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.468082101913506</v>
+        <v>2.587083745080684</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.254202547951678</v>
+        <v>-3.992502760934615</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9894658705395305</v>
+        <v>1.094145785346356</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3763687509435434</v>
+        <v>-0.1780326789982474</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.465682063467823</v>
+        <v>2.584683706635001</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.235164420244381</v>
+        <v>-3.973464633227318</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9936058408306945</v>
+        <v>1.09828575563752</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.434552362274738</v>
+        <v>-0.2362162903294419</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.427296615877351</v>
+        <v>2.546298259044529</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.391742440841397</v>
+        <v>3.845194132847282</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.251910285500756</v>
+        <v>-3.990210498483693</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.164489363666825</v>
+        <v>1.26916927847365</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.434552362274738</v>
+        <v>-0.2362162903294419</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.604878484816032</v>
+        <v>2.72388012798321</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240514.xlsx
+++ b/tame_output/ON/bt/strategyON_20240514.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>46.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-18.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.2%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.6%</t>
+          <t>113.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>131.9%</t>
+          <t>132.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.1%</t>
+          <t>-52.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.8%</t>
+          <t>448.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-560.6%</t>
+          <t>-575.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-42.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-169.9%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-249.3%</t>
+          <t>-255.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,16 +1242,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1285,11 +1285,11 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-464.2%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-182.8%</t>
+          <t>-246.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-247.6%</t>
+          <t>-257.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2024-05-14</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-173.6%</t>
+          <t>-153.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1963"/>
+  <dimension ref="A1:G1964"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382194</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900556660786</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880273</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.29911483439</v>
+        <v>-11.46121771111398</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.358248182618599</v>
+        <v>-1.423089333308192</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.936139185152558</v>
+        <v>-3.034878346804777</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.400070664359613</v>
+        <v>1.340827167368281</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.24709932042119</v>
+        <v>-11.40920219714517</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.333451641344673</v>
+        <v>-1.398292792034266</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.936139185152558</v>
+        <v>-3.034878346804777</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.404061000046014</v>
+        <v>1.344817503054682</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.38877116214531</v>
+        <v>-11.55087403886929</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.391595604933062</v>
+        <v>-1.456436755622656</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.936139185152558</v>
+        <v>-3.034878346804777</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.402585773147272</v>
+        <v>1.343342276155941</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.33918031772047</v>
+        <v>-11.50128319444445</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.356705856998257</v>
+        <v>-1.42154700768785</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.886548340727725</v>
+        <v>-2.985287502379943</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.447393689967045</v>
+        <v>1.388150192975713</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.14002821048337</v>
+        <v>-11.30213108720736</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.2900961477501</v>
+        <v>-1.354937298439693</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.721225814777911</v>
+        <v>-2.81996497643013</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.53353607189025</v>
+        <v>1.474292574898918</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.91418305776396</v>
+        <v>-11.07628593448795</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.190179013626127</v>
+        <v>-1.255020164315721</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.679299139190748</v>
+        <v>-2.778038300842967</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.568271150278756</v>
+        <v>1.509027653287425</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.78960440142637</v>
+        <v>-10.95170727815035</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.139208406535031</v>
+        <v>-1.204049557224625</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.679299139190748</v>
+        <v>-2.778038300842967</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.569410294834815</v>
+        <v>1.510166797843484</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.84249968947065</v>
+        <v>-11.00460256619464</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.157732747590638</v>
+        <v>-1.222573898280232</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.674343793102302</v>
+        <v>-2.77308295475452</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.575017276649991</v>
+        <v>1.515773779658659</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.55859095854191</v>
+        <v>-10.72069383526589</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.038435550980502</v>
+        <v>-1.103276701670096</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.674343793102302</v>
+        <v>-2.77308295475452</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.580750980888627</v>
+        <v>1.521507483897296</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.48722456593226</v>
+        <v>-10.64932744265624</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.019626256330509</v>
+        <v>-1.084467407020102</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.602977400492654</v>
+        <v>-2.701716562144873</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.613833554060551</v>
+        <v>1.554590057069219</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.22338769872819</v>
+        <v>-10.38549057545217</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.923974990761788</v>
+        <v>-0.9888161414513816</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.602977400492654</v>
+        <v>-2.701716562144873</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.603950072747643</v>
+        <v>1.544706575756312</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.956145897859791</v>
+        <v>-10.11824877458378</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8189128309138027</v>
+        <v>-0.8837539816033968</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.602977400492654</v>
+        <v>-2.701716562144873</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.602115512248269</v>
+        <v>1.542872015256938</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.858238859183301</v>
+        <v>-10.02034173590729</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.780050330416667</v>
+        <v>-0.8448914811062616</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.534991650632097</v>
+        <v>-2.633730812284316</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.642606647191142</v>
+        <v>1.583363150199811</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.834285318207343</v>
+        <v>-9.996388194931328</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7698004078807905</v>
+        <v>-0.8346415585703846</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.51103810965614</v>
+        <v>-2.609777271308359</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.65764727792221</v>
+        <v>1.598403780930879</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.570225379884546</v>
+        <v>-9.732328256608531</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6774367487134239</v>
+        <v>-0.7422778994030179</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.246978171333344</v>
+        <v>-2.345717332985563</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.802822924754136</v>
+        <v>1.743579427762805</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.863145756379708</v>
+        <v>-9.025248633103693</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3973919329717899</v>
+        <v>-0.4622330836613839</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.246978171333344</v>
+        <v>-2.345717332985563</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.800035891093835</v>
+        <v>1.740792394102504</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.822961458013518</v>
+        <v>-8.985064334737503</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3809745897374723</v>
+        <v>-0.4458157404270664</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.206793872967153</v>
+        <v>-2.305533034619372</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.824490094001391</v>
+        <v>1.765246597010059</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.742891662475714</v>
+        <v>-8.904994539199699</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3495798503015934</v>
+        <v>-0.4144210009911875</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.126724077429349</v>
+        <v>-2.225463239081568</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.87189879254483</v>
+        <v>1.812655295553499</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.509410440246114</v>
+        <v>-8.671513316970099</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2482629325719015</v>
+        <v>-0.3131040832614955</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.89324285519975</v>
+        <v>-1.991982016851969</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.019911954720442</v>
+        <v>1.960668457729111</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.3597440492386</v>
+        <v>-8.521846925962585</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1912885864818548</v>
+        <v>-0.2561297371714488</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.800339363957215</v>
+        <v>-1.899078525609433</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.072761839153004</v>
+        <v>2.013518342161673</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.227468575607713</v>
+        <v>-8.389571452331698</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1430109102824728</v>
+        <v>-0.2078520609720669</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.668063890326328</v>
+        <v>-1.766803051978547</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.147494610078563</v>
+        <v>2.088251113087232</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.036868900934559</v>
+        <v>-8.198971777658544</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.06395597972557487</v>
+        <v>-0.1287971304151689</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.477464215653175</v>
+        <v>-1.576203377305394</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.264669475570091</v>
+        <v>2.20542597857876</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.787869102250978</v>
+        <v>-7.949971978974963</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.04855028097151637</v>
+        <v>-0.01629086971807769</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.477464215653175</v>
+        <v>-1.576203377305394</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.27757581679375</v>
+        <v>2.218332319802419</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.893459092024083</v>
+        <v>-8.055561968748068</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1216616445369443</v>
+        <v>-0.1865027952265379</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.583054205426279</v>
+        <v>-1.681793367078498</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.086245893330669</v>
+        <v>2.027002396339338</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.91219399414268</v>
+        <v>-8.074296870866664</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.08061126350729664</v>
+        <v>-0.1454524141968907</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.583054205426279</v>
+        <v>-1.681793367078498</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.134790235207755</v>
+        <v>2.075546738216424</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.76425395273508</v>
+        <v>-7.926356829459065</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1413141696324245</v>
+        <v>-0.2061553203220186</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.562733289517722</v>
+        <v>-1.661472451169941</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.027103862064722</v>
+        <v>1.967860365073391</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.740025316346108</v>
+        <v>-7.902128193070093</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1403367013303134</v>
+        <v>-0.2051778520199075</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.538504653128749</v>
+        <v>-1.637243814780968</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.032927057644628</v>
+        <v>1.973683560653296</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.696476909575417</v>
+        <v>-7.858579786299402</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1298779507171304</v>
+        <v>-0.1947191014067244</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.538504653128749</v>
+        <v>-1.637243814780968</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.025966445549535</v>
+        <v>1.966722948558203</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.454328516121559</v>
+        <v>-7.616431392845544</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.01855623895444403</v>
+        <v>-0.08339738964403809</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.538504653128749</v>
+        <v>-1.637243814780968</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.040428799930678</v>
+        <v>1.981185302939346</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.391099144353211</v>
+        <v>-7.553202021077196</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.001267630212089976</v>
+        <v>-0.06357352047750364</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.538504653128749</v>
+        <v>-1.637243814780968</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.034960920389873</v>
+        <v>1.975717423398541</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.26780800953608</v>
+        <v>-7.429910886260065</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.04808217814951954</v>
+        <v>-0.01675897254007452</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.415213518311619</v>
+        <v>-1.513952679963838</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.106433695290728</v>
+        <v>2.047190198299396</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.246658810632637</v>
+        <v>-7.408761687356622</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.06424283594822189</v>
+        <v>-0.0005983147413721746</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.394064319408176</v>
+        <v>-1.492803481060395</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.126824192870119</v>
+        <v>2.067580695878787</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.002893368649192</v>
+        <v>-7.164996245373177</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1575297210886504</v>
+        <v>0.09268857039905631</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.394064319408176</v>
+        <v>-1.492803481060395</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.122604901217169</v>
+        <v>2.063361404225838</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.738865301455933</v>
+        <v>-6.900968178179918</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2652652618859701</v>
+        <v>0.200424111196376</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.192198920592222</v>
+        <v>-1.290938082244441</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.245848454426758</v>
+        <v>2.186604957435426</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.489014907506858</v>
+        <v>-6.651117784230843</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3579474944493022</v>
+        <v>0.2931063437597081</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.192198920592222</v>
+        <v>-1.290938082244441</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.23859052941046</v>
+        <v>2.179347032419129</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.313122815039426</v>
+        <v>-6.475225691763411</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4319034549569238</v>
+        <v>0.3670623042673298</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.192198920592222</v>
+        <v>-1.290938082244441</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.242189652931109</v>
+        <v>2.182946155939777</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.141676352016963</v>
+        <v>-6.303779228740948</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5138095462204628</v>
+        <v>0.4489683955308688</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.020752457569759</v>
+        <v>-1.119491619221978</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.35838503679914</v>
+        <v>2.299141539807809</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.77376164710278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.91664335234814</v>
+        <v>-6.078746229072125</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6028432237042889</v>
+        <v>0.5380020730146948</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.795719457900936</v>
+        <v>-0.8944586195531549</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.492425314216731</v>
+        <v>2.4331818172254</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.702008974711733</v>
+        <v>-5.864111851435718</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6933917758131689</v>
+        <v>0.6285506251235748</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5810850802645292</v>
+        <v>-0.6798242419167481</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.625900741852892</v>
+        <v>2.566657244861561</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.609008933505835</v>
+        <v>-5.77111181022982</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7117860510793239</v>
+        <v>0.6469449003897298</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5810850802645292</v>
+        <v>-0.6798242419167481</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.607095000636688</v>
+        <v>2.547851503645357</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.368578436700974</v>
+        <v>-5.530681313424959</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8097013264261452</v>
+        <v>0.7448601757365516</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.3406545834596689</v>
+        <v>-0.4393937451118878</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.753096375344481</v>
+        <v>2.69385287835315</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.29633586852978</v>
+        <v>-5.458438745253765</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8425276675294433</v>
+        <v>0.7776865168398497</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.3406545834596689</v>
+        <v>-0.4393937451118878</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.757025689179302</v>
+        <v>2.69778219218797</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.180396018904594</v>
+        <v>-5.342498895628579</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8895821912968578</v>
+        <v>0.8247410406072637</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.263832852443545</v>
+        <v>-0.3625720140957639</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.803797311706316</v>
+        <v>2.744553814714985</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.937740430481432</v>
+        <v>-5.099843307205417</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9836424978861162</v>
+        <v>0.9188013471965224</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.263832852443545</v>
+        <v>-0.3625720140957639</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.800795382926309</v>
+        <v>2.741551885934978</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.717719632444421</v>
+        <v>-4.879822509168406</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.073229854111535</v>
+        <v>1.008388703421941</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1226130073755648</v>
+        <v>-0.2213521690277837</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.887106326977712</v>
+        <v>2.82786282998638</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.584851943381143</v>
+        <v>-4.746954820105128</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.142271112538669</v>
+        <v>1.077429961849075</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1226130073755648</v>
+        <v>-0.2213521690277837</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.903000509779535</v>
+        <v>2.843757012788203</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.425336839861774</v>
+        <v>-4.587439716585759</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.207222998386719</v>
+        <v>1.142381847697125</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.03690209614380513</v>
+        <v>-0.06183706550841372</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.999855416331459</v>
+        <v>2.940611919340127</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.280664694762036</v>
+        <v>-4.442767571486021</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.275179958988053</v>
+        <v>1.21033880829846</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.1815742412435425</v>
+        <v>0.08283507959132369</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.096746805952741</v>
+        <v>3.03750330896141</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.340539522119728</v>
+        <v>-4.502642398843713</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.237267519446402</v>
+        <v>1.172426368756808</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1216994138858504</v>
+        <v>0.02296025223363157</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.046859400939552</v>
+        <v>2.98761590394822</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.25374002434072</v>
+        <v>-4.415842901064705</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.294387811880572</v>
+        <v>1.229546661190978</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1216994138858504</v>
+        <v>0.02296025223363157</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.069259894262118</v>
+        <v>3.010016397270786</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900692</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.256209730802526</v>
+        <v>-4.418312607526511</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.293472330669262</v>
+        <v>1.228631179979668</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1192297074240443</v>
+        <v>0.02049054577182541</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.067850471758446</v>
+        <v>3.008606974767115</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.324579917126536</v>
+        <v>-4.486682793850521</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.27713117861436</v>
+        <v>1.212290027924765</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1285054064602592</v>
+        <v>0.02976624480804035</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.084422813654877</v>
+        <v>3.025179316663546</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.20316348750006</v>
+        <v>-4.365266364224045</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.316134459096841</v>
+        <v>1.251293308407248</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1285054064602592</v>
+        <v>0.02976624480804035</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.074859522286769</v>
+        <v>3.015616025295437</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.234156646828765</v>
+        <v>-4.39625952355275</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.128446760405746</v>
+        <v>1.063605609716152</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1285054064602592</v>
+        <v>0.02976624480804035</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.899569087327155</v>
+        <v>2.840325590335824</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.058682387036296</v>
+        <v>-4.220785263760281</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.203203696314522</v>
+        <v>1.138362545624928</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1285054064602592</v>
+        <v>0.02976624480804035</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.904136319318943</v>
+        <v>2.844892822327612</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.169618639677545</v>
+        <v>-4.331721516401529</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.134571224019229</v>
+        <v>1.069730073329635</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1285054064602592</v>
+        <v>0.02976624480804035</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.87987834808015</v>
+        <v>2.820634851088819</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.372645217220778</v>
+        <v>-4.534748093944763</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.056491978221842</v>
+        <v>0.9916508275322475</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.07452117108297418</v>
+        <v>-0.173260332735193</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.761193786774116</v>
+        <v>2.701950289782785</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.214719618285485</v>
+        <v>-4.37682249500947</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.129834604228091</v>
+        <v>1.064993453538497</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.07452117108297418</v>
+        <v>-0.173260332735193</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.771366173206248</v>
+        <v>2.712122676214917</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.128476155259107</v>
+        <v>-4.290579031983092</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.159278260012502</v>
+        <v>1.094437109322909</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.07452117108297418</v>
+        <v>-0.173260332735193</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.766312443780108</v>
+        <v>2.707068946788777</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.129659239910168</v>
+        <v>-4.291762116634153</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.150580801596603</v>
+        <v>1.085739650907009</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.08016421954948572</v>
+        <v>-0.1789033812017046</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.754702390144727</v>
+        <v>2.695458893153396</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.006531532916085</v>
+        <v>-4.16863440964007</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.200383757427338</v>
+        <v>1.135542606737744</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.08016421954948572</v>
+        <v>-0.1789033812017046</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.755254263177828</v>
+        <v>2.696010766186497</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.913721051465226</v>
+        <v>-4.075823928189211</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.166780641899048</v>
+        <v>1.101939491209454</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.01264626190137363</v>
+        <v>-0.08609289975084522</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.74021324393971</v>
+        <v>2.680969746948378</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.865157999244196</v>
+        <v>-4.027260875968181</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.188079338712061</v>
+        <v>1.123238188022467</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.06120931412240382</v>
+        <v>-0.03752984752981503</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.771224551196929</v>
+        <v>2.711981054205598</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.752486781007946</v>
+        <v>-3.914589657731931</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.228223534518284</v>
+        <v>1.16338238382869</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.173880532358654</v>
+        <v>0.07514137070643517</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.833902990650402</v>
+        <v>2.774659493659071</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.640109779825273</v>
+        <v>-3.802212656549258</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.27866563082202</v>
+        <v>1.213824480132426</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.173880532358654</v>
+        <v>0.07514137070643517</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.839394286481069</v>
+        <v>2.780150789489738</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.68959426496886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.838344348712003</v>
+        <v>-4.000447225435988</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.210869005035867</v>
+        <v>1.146027854346273</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.02435403652807655</v>
+        <v>-0.1230931981802954</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.73195074691757</v>
+        <v>2.672707249926238</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.921345629737282</v>
+        <v>-4.083448506461267</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.016024212626409</v>
+        <v>0.9511830619368145</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.04292492105525031</v>
+        <v>-0.1416640827074692</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.559163936201919</v>
+        <v>2.499920439210587</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.682712735199267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.762151357680706</v>
+        <v>-3.924254234404691</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.199851582168245</v>
+        <v>1.135010431478651</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.04292492105525031</v>
+        <v>-0.1416640827074692</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.679313596921125</v>
+        <v>2.620070099929793</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660767</v>
+        <v>3.733008865660766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.848749940661809</v>
+        <v>-4.010852817385794</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.179725175078126</v>
+        <v>1.114884024388532</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.04292492105525031</v>
+        <v>-0.1416640827074692</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.693826623023448</v>
+        <v>2.634583126032116</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.810366278103658</v>
+        <v>-3.972469154827643</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.192498081443756</v>
+        <v>1.127656930754161</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.004541258497099132</v>
+        <v>-0.103280420149318</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.714276261900707</v>
+        <v>2.655032764909376</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002483</v>
+        <v>3.751143622002482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.633249948068492</v>
+        <v>-3.795352824792477</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.260073642303124</v>
+        <v>1.19523249161353</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.004541258497099132</v>
+        <v>-0.103280420149318</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.711005290746009</v>
+        <v>2.651761793754678</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263901</v>
+        <v>3.7413248732639</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.603547824092198</v>
+        <v>-3.765650700816184</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.272637883655555</v>
+        <v>1.20779673296596</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.009011383712412502</v>
+        <v>-0.1077505453646314</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.709006607378734</v>
+        <v>2.649763110387402</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481235</v>
+        <v>3.750725801481234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.42417240285343</v>
+        <v>-3.586275279577416</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.338175027457476</v>
+        <v>1.273333876767882</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1477653744583062</v>
+        <v>0.04902621280608732</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.796859637587579</v>
+        <v>2.737616140596248</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.469186616374036</v>
+        <v>-3.631289493098022</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.300976797380823</v>
+        <v>1.236135646691229</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1174164791437016</v>
+        <v>0.01867731749148271</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.759457755730407</v>
+        <v>2.700214258739075</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979537</v>
+        <v>3.737023032979536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.736191126646472</v>
+        <v>-3.898294003370458</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.199866555610795</v>
+        <v>1.135025404921201</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.07694655889924701</v>
+        <v>-0.1756857205514659</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.648531495243583</v>
+        <v>2.589287998252252</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230806</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.024978347105387</v>
+        <v>-4.187081223829373</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.08355558932373</v>
+        <v>1.018714438634136</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1780326789982474</v>
+        <v>-0.2767718406504662</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.587083745080684</v>
+        <v>2.527840248089353</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285452</v>
+        <v>3.705568086285451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.992502760934615</v>
+        <v>-4.154605637658601</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.094145785346356</v>
+        <v>1.029304634656762</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1780326789982474</v>
+        <v>-0.2767718406504662</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.584683706635001</v>
+        <v>2.52544020964367</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095068678481</v>
+        <v>3.709506867848099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.973464633227318</v>
+        <v>-4.135567509951303</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.09828575563752</v>
+        <v>1.033444604947925</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2362162903294419</v>
+        <v>-0.3349554519816608</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.546298259044529</v>
+        <v>2.487054762053198</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,45 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.845194132847282</v>
+        <v>3.731060897601247</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.990210498483693</v>
+        <v>-4.135751133116614</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.26916927847365</v>
+        <v>1.210953024620482</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2362162903294419</v>
+        <v>-0.3349554519816608</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.72388012798321</v>
+        <v>2.664636630991879</v>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" s="2" t="n">
+        <v>45426</v>
+      </c>
+      <c r="B1964" t="n">
+        <v>3.746640094144097</v>
+      </c>
+      <c r="C1964" t="n">
+        <v>2.930648445733344</v>
+      </c>
+      <c r="D1964" t="n">
+        <v>-4.135751133116614</v>
+      </c>
+      <c r="E1964" t="n">
+        <v>1.210953024620482</v>
+      </c>
+      <c r="F1964" t="n">
+        <v>-0.3349554519816608</v>
+      </c>
+      <c r="G1964" t="n">
+        <v>2.923712242719712</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240514.xlsx
+++ b/tame_output/ON/bt/strategyON_20240514.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>56.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-6.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-77.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>112.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.6%</t>
+          <t>131.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.7%</t>
+          <t>-52.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.8%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.4%</t>
+          <t>448.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-575.1%</t>
+          <t>-569.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.3%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-237.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-255.1%</t>
+          <t>-252.8%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-32.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-246.8%</t>
+          <t>-194.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-257.5%</t>
+          <t>-257.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-24</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-153.7%</t>
+          <t>-141.3%</t>
         </is>
       </c>
     </row>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382194</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.46121771111398</v>
+        <v>-11.28675108925061</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.423089333308192</v>
+        <v>-1.353302684562845</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.034878346804777</v>
+        <v>-2.938452661292489</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.340827167368281</v>
+        <v>1.398682578675655</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.40920219714517</v>
+        <v>-11.2347355752818</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.398292792034266</v>
+        <v>-1.328506143288919</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.034878346804777</v>
+        <v>-2.938452661292489</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.344817503054682</v>
+        <v>1.402672914362056</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.55087403886929</v>
+        <v>-11.37640741700592</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.456436755622656</v>
+        <v>-1.386650106877309</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.034878346804777</v>
+        <v>-2.938452661292489</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.343342276155941</v>
+        <v>1.401197687463314</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.50128319444445</v>
+        <v>-11.32681657258109</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.42154700768785</v>
+        <v>-1.351760358942503</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.985287502379943</v>
+        <v>-2.888861816867655</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.388150192975713</v>
+        <v>1.446005604283086</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.30213108720736</v>
+        <v>-11.12766446534399</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.354937298439693</v>
+        <v>-1.285150649694347</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.81996497643013</v>
+        <v>-2.723539290917842</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.474292574898918</v>
+        <v>1.532147986206291</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.07628593448795</v>
+        <v>-10.90181931262458</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.255020164315721</v>
+        <v>-1.185233515570374</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.778038300842967</v>
+        <v>-2.681612615330678</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.509027653287425</v>
+        <v>1.566883064594798</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.95170727815035</v>
+        <v>-10.77724065628699</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.204049557224625</v>
+        <v>-1.134262908479279</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.778038300842967</v>
+        <v>-2.681612615330678</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.510166797843484</v>
+        <v>1.568022209150857</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.00460256619464</v>
+        <v>-10.83013594433127</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.222573898280232</v>
+        <v>-1.152787249534885</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.77308295475452</v>
+        <v>-2.676657269242232</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.515773779658659</v>
+        <v>1.573629190966032</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081567</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.72069383526589</v>
+        <v>-10.54622721340252</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.103276701670096</v>
+        <v>-1.033490052924749</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.77308295475452</v>
+        <v>-2.676657269242232</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.521507483897296</v>
+        <v>1.579362895204669</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.64932744265624</v>
+        <v>-10.47486082079288</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.084467407020102</v>
+        <v>-1.014680758274755</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.701716562144873</v>
+        <v>-2.605290876632584</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.554590057069219</v>
+        <v>1.612445468376593</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.38549057545217</v>
+        <v>-10.21102395358881</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9888161414513816</v>
+        <v>-0.9190294927060356</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.701716562144873</v>
+        <v>-2.605290876632584</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.544706575756312</v>
+        <v>1.602561987063685</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906226</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.11824877458378</v>
+        <v>-9.943782152720409</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8837539816033968</v>
+        <v>-0.8139673328580499</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.701716562144873</v>
+        <v>-2.605290876632584</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.542872015256938</v>
+        <v>1.600727426564311</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.02034173590729</v>
+        <v>-9.845875114043919</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8448914811062616</v>
+        <v>-0.7751048323609147</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.633730812284316</v>
+        <v>-2.537305126772027</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.583363150199811</v>
+        <v>1.641218561507184</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.996388194931328</v>
+        <v>-9.821921573067961</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8346415585703846</v>
+        <v>-0.7648549098250377</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.609777271308359</v>
+        <v>-2.51335158579607</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.598403780930879</v>
+        <v>1.656259192238252</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.732328256608531</v>
+        <v>-9.557861634745164</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7422778994030179</v>
+        <v>-0.672491250657671</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.345717332985563</v>
+        <v>-2.249291647473274</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.743579427762805</v>
+        <v>1.801434839070178</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309725</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.025248633103693</v>
+        <v>-8.850782011240327</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4622330836613839</v>
+        <v>-0.392446434916037</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.345717332985563</v>
+        <v>-2.249291647473274</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.740792394102504</v>
+        <v>1.798647805409877</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.985064334737503</v>
+        <v>-8.810597712874136</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4458157404270664</v>
+        <v>-0.3760290916817195</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.305533034619372</v>
+        <v>-2.209107349107083</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.765246597010059</v>
+        <v>1.823102008317433</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096474</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.904994539199699</v>
+        <v>-8.730527917336332</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4144210009911875</v>
+        <v>-0.3446343522458406</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.225463239081568</v>
+        <v>-2.129037553569279</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.812655295553499</v>
+        <v>1.870510706860872</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.671513316970099</v>
+        <v>-8.497046695106732</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3131040832614955</v>
+        <v>-0.2433174345161486</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.991982016851969</v>
+        <v>-1.895556331339681</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.960668457729111</v>
+        <v>2.018523869036484</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.521846925962585</v>
+        <v>-8.347380304099218</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2561297371714488</v>
+        <v>-0.1863430884261019</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.899078525609433</v>
+        <v>-1.802652840097145</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.013518342161673</v>
+        <v>2.071373753469046</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.389571452331698</v>
+        <v>-8.215104830468331</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2078520609720669</v>
+        <v>-0.13806541222672</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.766803051978547</v>
+        <v>-1.670377366466258</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.088251113087232</v>
+        <v>2.146106524394605</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.198971777658544</v>
+        <v>-8.024505155795177</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1287971304151689</v>
+        <v>-0.05901048166982203</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.576203377305394</v>
+        <v>-1.479777691793105</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.20542597857876</v>
+        <v>2.263281389886133</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.949971978974963</v>
+        <v>-7.775505357111596</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.01629086971807769</v>
+        <v>0.05349577902726921</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.576203377305394</v>
+        <v>-1.479777691793105</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.218332319802419</v>
+        <v>2.276187731109792</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.055561968748068</v>
+        <v>-7.881095346884701</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1865027952265379</v>
+        <v>-0.1167161464811914</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.681793367078498</v>
+        <v>-1.585367681566209</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.027002396339338</v>
+        <v>2.084857807646711</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.074296870866664</v>
+        <v>-7.899830249003298</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1454524141968907</v>
+        <v>-0.0756657654515438</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.681793367078498</v>
+        <v>-1.585367681566209</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.075546738216424</v>
+        <v>2.133402149523797</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.926356829459065</v>
+        <v>-7.751890207595698</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2061553203220186</v>
+        <v>-0.1363686715766717</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.661472451169941</v>
+        <v>-1.565046765657652</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.967860365073391</v>
+        <v>2.025715776380764</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.902128193070093</v>
+        <v>-7.727661571206726</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2051778520199075</v>
+        <v>-0.135391203274561</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.637243814780968</v>
+        <v>-1.54081812926868</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.973683560653296</v>
+        <v>2.03153897196067</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.858579786299402</v>
+        <v>-7.684113164436035</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1947191014067244</v>
+        <v>-0.124932452661378</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.637243814780968</v>
+        <v>-1.54081812926868</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.966722948558203</v>
+        <v>2.024578359865576</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.616431392845544</v>
+        <v>-7.441964770982177</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.08339738964403809</v>
+        <v>-0.01361074089869163</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.637243814780968</v>
+        <v>-1.54081812926868</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.981185302939346</v>
+        <v>2.03904071424672</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.553202021077196</v>
+        <v>-7.378735399213829</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.06357352047750364</v>
+        <v>0.006213128267842816</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.637243814780968</v>
+        <v>-1.54081812926868</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.975717423398541</v>
+        <v>2.033572834705915</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.429910886260065</v>
+        <v>-7.255444264396698</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.01675897254007452</v>
+        <v>0.05302767620527193</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.513952679963838</v>
+        <v>-1.417526994451549</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.047190198299396</v>
+        <v>2.10504560960677</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.408761687356622</v>
+        <v>-7.234295065493255</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.0005983147413721746</v>
+        <v>0.06918833400397473</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.492803481060395</v>
+        <v>-1.396377795548106</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.067580695878787</v>
+        <v>2.125436107186161</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.164996245373177</v>
+        <v>-6.99052962350981</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.09268857039905631</v>
+        <v>0.1624752191444032</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.492803481060395</v>
+        <v>-1.396377795548106</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.063361404225838</v>
+        <v>2.121216815533211</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.900968178179918</v>
+        <v>-6.726501556316551</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.200424111196376</v>
+        <v>0.2702107599417229</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.290938082244441</v>
+        <v>-1.194512396732152</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.186604957435426</v>
+        <v>2.2444603687428</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749182</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.651117784230843</v>
+        <v>-6.476651162367476</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2931063437597081</v>
+        <v>0.362892992505055</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.290938082244441</v>
+        <v>-1.194512396732152</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.179347032419129</v>
+        <v>2.237202443726502</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481495</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.475225691763411</v>
+        <v>-6.300759069900044</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3670623042673298</v>
+        <v>0.4368489530126762</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.290938082244441</v>
+        <v>-1.194512396732152</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.182946155939777</v>
+        <v>2.24080156724715</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862985</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.303779228740948</v>
+        <v>-6.129312606877581</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4489683955308688</v>
+        <v>0.5187550442762157</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.119491619221978</v>
+        <v>-1.023065933709689</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.299141539807809</v>
+        <v>2.356996951115182</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376164710278</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.078746229072125</v>
+        <v>-5.904279607208758</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5380020730146948</v>
+        <v>0.6077887217600417</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8944586195531549</v>
+        <v>-0.7980329340408662</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.4331818172254</v>
+        <v>2.491037228532773</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.864111851435718</v>
+        <v>-5.689645229572351</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6285506251235748</v>
+        <v>0.6983372738689217</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6798242419167481</v>
+        <v>-0.5833985564044594</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.566657244861561</v>
+        <v>2.624512656168934</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.77111181022982</v>
+        <v>-5.596645188366453</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6469449003897298</v>
+        <v>0.7167315491350768</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6798242419167481</v>
+        <v>-0.5833985564044594</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.547851503645357</v>
+        <v>2.60570691495273</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.530681313424959</v>
+        <v>-5.356214691561592</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7448601757365516</v>
+        <v>0.8146468244818981</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4393937451118878</v>
+        <v>-0.3429680595995991</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.69385287835315</v>
+        <v>2.751708289660523</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.458438745253765</v>
+        <v>-5.283972123390398</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7776865168398497</v>
+        <v>0.8474731655851961</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4393937451118878</v>
+        <v>-0.3429680595995991</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.69778219218797</v>
+        <v>2.755637603495344</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.342498895628579</v>
+        <v>-5.168032273765212</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8247410406072637</v>
+        <v>0.8945276893526102</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3625720140957639</v>
+        <v>-0.2661463285834752</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.744553814714985</v>
+        <v>2.802409226022358</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.099843307205417</v>
+        <v>-4.92537668534205</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9188013471965224</v>
+        <v>0.9885879959418689</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3625720140957639</v>
+        <v>-0.2661463285834752</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.741551885934978</v>
+        <v>2.799407297242351</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.879822509168406</v>
+        <v>-4.705355887305039</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.008388703421941</v>
+        <v>1.078175352167287</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2213521690277837</v>
+        <v>-0.124926483515495</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.82786282998638</v>
+        <v>2.885718241293754</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.746954820105128</v>
+        <v>-4.572488198241762</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.077429961849075</v>
+        <v>1.147216610594422</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2213521690277837</v>
+        <v>-0.124926483515495</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.843757012788203</v>
+        <v>2.901612424095577</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.587439716585759</v>
+        <v>-4.412973094722392</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.142381847697125</v>
+        <v>1.212168496442471</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.06183706550841372</v>
+        <v>0.03458862000387497</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.940611919340127</v>
+        <v>2.998467330647501</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.442767571486021</v>
+        <v>-4.268300949622654</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.21033880829846</v>
+        <v>1.280125457043806</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.08283507959132369</v>
+        <v>0.1792607651036124</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.03750330896141</v>
+        <v>3.095358720268783</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.502642398843713</v>
+        <v>-4.328175776980347</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.172426368756808</v>
+        <v>1.242213017502155</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.02296025223363157</v>
+        <v>0.1193859377459203</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.98761590394822</v>
+        <v>3.045471315255594</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144515</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.415842901064705</v>
+        <v>-4.241376279201338</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.229546661190978</v>
+        <v>1.299333309936325</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.02296025223363157</v>
+        <v>0.1193859377459203</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.010016397270786</v>
+        <v>3.06787180857816</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900692</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.418312607526511</v>
+        <v>-4.243845985663144</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.228631179979668</v>
+        <v>1.298417828725014</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.02049054577182541</v>
+        <v>0.1169162312841141</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.008606974767115</v>
+        <v>3.066462386074488</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.486682793850521</v>
+        <v>-4.312216171987155</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.212290027924765</v>
+        <v>1.282076676670112</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.126191930320329</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.025179316663546</v>
+        <v>3.083034727970919</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.365266364224045</v>
+        <v>-4.190799742360678</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.251293308407248</v>
+        <v>1.321079957152594</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.126191930320329</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.015616025295437</v>
+        <v>3.07347143660281</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.39625952355275</v>
+        <v>-4.221792901689383</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.063605609716152</v>
+        <v>1.133392258461499</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.126191930320329</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.840325590335824</v>
+        <v>2.898181001643197</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.220785263760281</v>
+        <v>-4.046318641896914</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.138362545624928</v>
+        <v>1.208149194370274</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.126191930320329</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.844892822327612</v>
+        <v>2.902748233634985</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.331721516401529</v>
+        <v>-4.157254894538163</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.069730073329635</v>
+        <v>1.139516722074982</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.126191930320329</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.820634851088819</v>
+        <v>2.878490262396192</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.534748093944763</v>
+        <v>-4.360281472081396</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9916508275322475</v>
+        <v>1.061437476277594</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.173260332735193</v>
+        <v>-0.07683464722290434</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.701950289782785</v>
+        <v>2.759805701090158</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.37682249500947</v>
+        <v>-4.202355873146103</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.064993453538497</v>
+        <v>1.134780102283844</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.173260332735193</v>
+        <v>-0.07683464722290434</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.712122676214917</v>
+        <v>2.76997808752229</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.290579031983092</v>
+        <v>-4.116112410119725</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.094437109322909</v>
+        <v>1.164223758068255</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.173260332735193</v>
+        <v>-0.07683464722290434</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.707068946788777</v>
+        <v>2.76492435809615</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.291762116634153</v>
+        <v>-4.117295494770786</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.085739650907009</v>
+        <v>1.155526299652356</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1789033812017046</v>
+        <v>-0.08247769568941588</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.695458893153396</v>
+        <v>2.753314304460769</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.16863440964007</v>
+        <v>-3.994167787776703</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.135542606737744</v>
+        <v>1.205329255483091</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1789033812017046</v>
+        <v>-0.08247769568941588</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.696010766186497</v>
+        <v>2.75386617749387</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.075823928189211</v>
+        <v>-3.901357306325844</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.101939491209454</v>
+        <v>1.1717261399548</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.08609289975084522</v>
+        <v>0.01033278576144347</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.680969746948378</v>
+        <v>2.738825158255751</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.027260875968181</v>
+        <v>-3.852794254104814</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.123238188022467</v>
+        <v>1.193024836767813</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.03752984752981503</v>
+        <v>0.05889583798247366</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.711981054205598</v>
+        <v>2.769836465512971</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.914589657731931</v>
+        <v>-3.839719946161641</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.16338238382869</v>
+        <v>1.193330268456805</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.07514137070643517</v>
+        <v>0.07197014592564666</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.774659493659071</v>
+        <v>2.772756758790597</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.802212656549258</v>
+        <v>-3.727342944978969</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.213824480132426</v>
+        <v>1.243772364760542</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.07514137070643517</v>
+        <v>0.07197014592564666</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.780150789489738</v>
+        <v>2.778248054621264</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959426496886</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.000447225435988</v>
+        <v>-3.925577513865699</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.146027854346273</v>
+        <v>1.175975738974389</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1230931981802954</v>
+        <v>-0.1262644229610839</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.672707249926238</v>
+        <v>2.670804515057765</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.083448506461267</v>
+        <v>-4.008578794890978</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9511830619368145</v>
+        <v>0.9811309465649303</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1416640827074692</v>
+        <v>-0.1448353074882577</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.499920439210587</v>
+        <v>2.498017704342114</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199267</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.924254234404691</v>
+        <v>-3.849384522834402</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.135010431478651</v>
+        <v>1.164958316106766</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1416640827074692</v>
+        <v>-0.1448353074882577</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.620070099929793</v>
+        <v>2.61816736506132</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660766</v>
+        <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.010852817385794</v>
+        <v>-3.935983105815505</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.114884024388532</v>
+        <v>1.144831909016648</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1416640827074692</v>
+        <v>-0.1448353074882577</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.634583126032116</v>
+        <v>2.632680391163643</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383422</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.972469154827643</v>
+        <v>-3.897599443257354</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.127656930754161</v>
+        <v>1.157604815382277</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.103280420149318</v>
+        <v>-0.1064516449301065</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.655032764909376</v>
+        <v>2.653130030040902</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002482</v>
+        <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.795352824792477</v>
+        <v>-3.720483113222187</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.19523249161353</v>
+        <v>1.225180376241646</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.103280420149318</v>
+        <v>-0.1064516449301065</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.651761793754678</v>
+        <v>2.649859058886204</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.7413248732639</v>
+        <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.765650700816184</v>
+        <v>-3.690780989245894</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.20779673296596</v>
+        <v>1.237744617594076</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1077505453646314</v>
+        <v>-0.1109217701454199</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.649763110387402</v>
+        <v>2.647860375518929</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481234</v>
+        <v>3.750725801481235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.586275279577416</v>
+        <v>-3.511405568007126</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.273333876767882</v>
+        <v>1.303281761395998</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.04902621280608732</v>
+        <v>0.0458549880252988</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.737616140596248</v>
+        <v>2.735713405727775</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452229</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.631289493098022</v>
+        <v>-3.556419781527732</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.236135646691229</v>
+        <v>1.266083531319345</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.01867731749148271</v>
+        <v>0.0155060927106942</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.700214258739075</v>
+        <v>2.698311523870602</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979536</v>
+        <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.898294003370458</v>
+        <v>-3.823424291800167</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.135025404921201</v>
+        <v>1.164973289549317</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1756857205514659</v>
+        <v>-0.1788569453322544</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.589287998252252</v>
+        <v>2.587385263383779</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.187081223829373</v>
+        <v>-4.112211512259083</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.018714438634136</v>
+        <v>1.048662323262252</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2767718406504662</v>
+        <v>-0.2799430654312547</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.527840248089353</v>
+        <v>2.52593751322088</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285451</v>
+        <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.154605637658601</v>
+        <v>-4.07973592608831</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.029304634656762</v>
+        <v>1.059252519284878</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2767718406504662</v>
+        <v>-0.2799430654312547</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.52544020964367</v>
+        <v>2.523537474775197</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848099</v>
+        <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.135567509951303</v>
+        <v>-4.060697798381013</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.033444604947925</v>
+        <v>1.063392489576041</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3349554519816608</v>
+        <v>-0.3381266767624493</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.487054762053198</v>
+        <v>2.485152027184724</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.135751133116614</v>
+        <v>-4.077443663637388</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.210953024620482</v>
+        <v>1.234276012412172</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3349554519816608</v>
+        <v>-0.3381266767624493</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.664636630991879</v>
+        <v>2.662733896123405</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.746640094144097</v>
+        <v>3.842786006525358</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.930648445733344</v>
+        <v>3.054078350717629</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.135751133116614</v>
+        <v>-4.077443663637388</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.210953024620482</v>
+        <v>1.234276012412172</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3349554519816608</v>
+        <v>-0.3381266767624493</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.923712242719712</v>
+        <v>3.047142147703997</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240514.xlsx
+++ b/tame_output/ON/bt/strategyON_20240514.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>30.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-25.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.6%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.5%</t>
+          <t>112.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>131.8%</t>
+          <t>132.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-697.2%</t>
+          <t>-706.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.1%</t>
+          <t>-52.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.7%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.6%</t>
+          <t>445.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.1%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-569.3%</t>
+          <t>-570.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-279.3%</t>
+          <t>-283.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-42.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-237.8%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-252.8%</t>
+          <t>-253.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.5%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.3%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>-462.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-194.2%</t>
+          <t>-183.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-257.8%</t>
+          <t>-247.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-141.3%</t>
+          <t>-160.1%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6452155037515721</v>
+        <v>-0.7393852932076951</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.86288613651235</v>
+        <v>2.825218220729901</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.852781288143184</v>
+        <v>-0.946951077599307</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.777684618874945</v>
+        <v>2.740016703092496</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.270535311690021</v>
+        <v>-1.364705101146144</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.608509900961274</v>
+        <v>2.570841985178824</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.492157245248138</v>
+        <v>-1.586327034704262</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.519727344136949</v>
+        <v>2.482059428354499</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9143710060726489</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.700161303601216</v>
+        <v>-1.794331093057339</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.441417865349643</v>
+        <v>2.403749949567194</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9143710060726489</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.911573724489191</v>
+        <v>-2.005743513945314</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.351934353332441</v>
+        <v>2.314266437549992</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7029585851846738</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.250732102077713</v>
+        <v>-2.344901891533836</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.209355301603481</v>
+        <v>2.171687385821032</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3638002075961517</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.459222883529397</v>
+        <v>-2.553392672985521</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.146297278761576</v>
+        <v>2.108629362979126</v>
       </c>
       <c r="F1852" t="n">
         <v>0.1553094261444673</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.952547755064575</v>
+        <v>-3.046717544520699</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.957066080556073</v>
+        <v>1.919398164773623</v>
       </c>
       <c r="F1853" t="n">
         <v>0.05032331190484857</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.444932783088672</v>
+        <v>-3.539102572544796</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.761218461390166</v>
+        <v>1.723550545607717</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.4420617161192482</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.830113174018745</v>
+        <v>-3.924282963474868</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.605688843831001</v>
+        <v>1.568020928048551</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.4420617161192482</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.173795947245408</v>
+        <v>-4.267965736701531</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.469984857994952</v>
+        <v>1.432316942212502</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.5499677681464663</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.380307724132429</v>
+        <v>-4.474477513588552</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.383486205896401</v>
+        <v>1.345818290113952</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.7564795450334878</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.68954182712848</v>
+        <v>-4.783711616584603</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.26156549139824</v>
+        <v>1.223897575615791</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.7564795450334878</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.121347620278267</v>
+        <v>-5.215517409734391</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.07517606160573</v>
+        <v>1.03750814582328</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8928970414747548</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.356041614410819</v>
+        <v>-5.450211403866943</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9695832389547996</v>
+        <v>0.9319153231723503</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8865607742454996</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.691704261641272</v>
+        <v>-5.785874051097395</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8338987717185837</v>
+        <v>0.7962308559361344</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8865607742454996</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.055330506541585</v>
+        <v>-6.149500295997709</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6949358339926999</v>
+        <v>0.6572679182102505</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9847824111126254</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.420457889180332</v>
+        <v>-6.514627678636455</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5481393959430325</v>
+        <v>0.5104714801605832</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.281093195411638</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.829046666361011</v>
+        <v>-6.923216455817133</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3834654290855202</v>
+        <v>0.3457975133030708</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.689681972592316</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.242029150502105</v>
+        <v>-7.336198939958227</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.213457867900543</v>
+        <v>0.1757899521180941</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.689681972592316</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.658421024789102</v>
+        <v>-7.752590814245225</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.0448951687946213</v>
+        <v>0.007227253012172419</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.689681972592316</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.035098035318946</v>
+        <v>-8.129267824775068</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.09551694474863703</v>
+        <v>-0.1331848605310859</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.689681972592316</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.380972857303755</v>
+        <v>-8.475142646759878</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2377673083968657</v>
+        <v>-0.2754352241793145</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.689681972592316</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.544552735488139</v>
+        <v>-8.638722524944262</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3047943396156181</v>
+        <v>-0.3424622553980674</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.689681972592316</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.841214077298337</v>
+        <v>-8.93538386675446</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4196799004104892</v>
+        <v>-0.4573478161929385</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.758425108326195</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.964458466513767</v>
+        <v>-9.058628255969889</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4730039606310643</v>
+        <v>-0.5106718764135132</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.758425108326195</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.347459855256398</v>
+        <v>-9.441629644712521</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6263066174497007</v>
+        <v>-0.6639745332321496</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.758425108326195</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.504858735469519</v>
+        <v>-9.599028524925641</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.686694653563519</v>
+        <v>-0.7243625693459679</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.915823988539316</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.86438905797352</v>
+        <v>-9.958558847429643</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8251564792670694</v>
+        <v>-0.8628243950495182</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.915823988539316</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.914738121427742</v>
+        <v>-10.00890791088387</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8373800846915809</v>
+        <v>-0.8750480004740298</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.966173051993538</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.13388708950194</v>
+        <v>-10.22805687895806</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9219979212994907</v>
+        <v>-0.9596658370819395</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.185322020067736</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.13019616454553</v>
+        <v>-10.22436595400165</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9205215513169267</v>
+        <v>-0.9581894670993756</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.185322020067736</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.33445433987539</v>
+        <v>-10.42862412933152</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9967116243302296</v>
+        <v>-1.034379540112679</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.312960964681725</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.55249211150657</v>
+        <v>-10.64666190096269</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.079444178498264</v>
+        <v>-1.117112094280714</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.487731732777624</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.47902227983912</v>
+        <v>-10.57319206929524</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.034684544337864</v>
+        <v>-1.072352460120313</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.414261901110175</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900556660786</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.65414669722566</v>
+        <v>-10.74831648668179</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.090179090544964</v>
+        <v>-1.127847006327413</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.589386318496719</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880273</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.88859879124015</v>
+        <v>-10.98276858069628</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.191179093052356</v>
+        <v>-1.228847008834805</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.589386318496719</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.17640263577739</v>
+        <v>-11.27057242523352</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.312972821641228</v>
+        <v>-1.350640737423677</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.877190163033957</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.22918879137772</v>
+        <v>-11.32335858083384</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.332971494042802</v>
+        <v>-1.370639409825252</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.972865649616354</v>
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.28675108925061</v>
+        <v>-11.39328462384612</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.353302684562845</v>
+        <v>-1.395916098401048</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.938452661292489</v>
+        <v>-2.936139185152558</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.398682578675655</v>
+        <v>1.400070664359613</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.2347355752818</v>
+        <v>-11.34126910987731</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.328506143288919</v>
+        <v>-1.371119557127122</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.938452661292489</v>
+        <v>-2.936139185152558</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.402672914362056</v>
+        <v>1.404061000046014</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.37640741700592</v>
+        <v>-11.48294095160143</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.386650106877309</v>
+        <v>-1.429263520715512</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.938452661292489</v>
+        <v>-2.936139185152558</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.401197687463314</v>
+        <v>1.402585773147272</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.32681657258109</v>
+        <v>-11.43335010717659</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.351760358942503</v>
+        <v>-1.394373772780706</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.888861816867655</v>
+        <v>-2.886548340727725</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.446005604283086</v>
+        <v>1.447393689967045</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.12766446534399</v>
+        <v>-11.23419799993949</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.285150649694347</v>
+        <v>-1.32776406353255</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.723539290917842</v>
+        <v>-2.721225814777911</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.532147986206291</v>
+        <v>1.53353607189025</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.90181931262458</v>
+        <v>-11.00835284722008</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.185233515570374</v>
+        <v>-1.227846929408577</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.681612615330678</v>
+        <v>-2.679299139190748</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.566883064594798</v>
+        <v>1.568271150278756</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.77724065628699</v>
+        <v>-10.88377419088249</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.134262908479279</v>
+        <v>-1.176876322317481</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.681612615330678</v>
+        <v>-2.679299139190748</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.568022209150857</v>
+        <v>1.569410294834815</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.83013594433127</v>
+        <v>-10.93666947892678</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.152787249534885</v>
+        <v>-1.195400663373088</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.676657269242232</v>
+        <v>-2.674343793102302</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.573629190966032</v>
+        <v>1.575017276649991</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.54622721340252</v>
+        <v>-10.65276074799803</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.033490052924749</v>
+        <v>-1.076103466762952</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.676657269242232</v>
+        <v>-2.674343793102302</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.579362895204669</v>
+        <v>1.580750980888627</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.47486082079288</v>
+        <v>-10.58139435538838</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.014680758274755</v>
+        <v>-1.057294172112958</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.605290876632584</v>
+        <v>-2.602977400492654</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.612445468376593</v>
+        <v>1.613833554060551</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.21102395358881</v>
+        <v>-10.31755748818431</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9190294927060356</v>
+        <v>-0.9616429065442378</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.605290876632584</v>
+        <v>-2.602977400492654</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.602561987063685</v>
+        <v>1.603950072747643</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.943782152720409</v>
+        <v>-10.05031568731592</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8139673328580499</v>
+        <v>-0.8565807466962521</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.605290876632584</v>
+        <v>-2.602977400492654</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.600727426564311</v>
+        <v>1.602115512248269</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.845875114043919</v>
+        <v>-9.952408648639425</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7751048323609147</v>
+        <v>-0.8177182461991168</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.537305126772027</v>
+        <v>-2.534991650632097</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.641218561507184</v>
+        <v>1.642606647191142</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.821921573067961</v>
+        <v>-9.928455107663467</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7648549098250377</v>
+        <v>-0.8074683236632403</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.51335158579607</v>
+        <v>-2.51103810965614</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.656259192238252</v>
+        <v>1.65764727792221</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.557861634745164</v>
+        <v>-9.66439516934067</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.672491250657671</v>
+        <v>-0.7151046644958736</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.249291647473274</v>
+        <v>-2.246978171333344</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.801434839070178</v>
+        <v>1.802822924754136</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.850782011240327</v>
+        <v>-8.957315545835833</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.392446434916037</v>
+        <v>-0.4350598487542396</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.249291647473274</v>
+        <v>-2.246978171333344</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.798647805409877</v>
+        <v>1.800035891093835</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.810597712874136</v>
+        <v>-8.917131247469642</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3760290916817195</v>
+        <v>-0.4186425055199221</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.209107349107083</v>
+        <v>-2.206793872967153</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.823102008317433</v>
+        <v>1.824490094001391</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.730527917336332</v>
+        <v>-8.837061451931838</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3446343522458406</v>
+        <v>-0.3872477660840432</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.129037553569279</v>
+        <v>-2.126724077429349</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.870510706860872</v>
+        <v>1.87189879254483</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.497046695106732</v>
+        <v>-8.603580229702239</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2433174345161486</v>
+        <v>-0.2859308483543512</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.895556331339681</v>
+        <v>-1.89324285519975</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.018523869036484</v>
+        <v>2.019911954720442</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.347380304099218</v>
+        <v>-8.453913838694724</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1863430884261019</v>
+        <v>-0.2289565022643045</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.802652840097145</v>
+        <v>-1.800339363957215</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.071373753469046</v>
+        <v>2.072761839153004</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.215104830468331</v>
+        <v>-8.321638365063837</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.13806541222672</v>
+        <v>-0.1806788260649226</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.670377366466258</v>
+        <v>-1.668063890326328</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.146106524394605</v>
+        <v>2.147494610078563</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.024505155795177</v>
+        <v>-8.131038690390683</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.05901048166982203</v>
+        <v>-0.1016238955080246</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.479777691793105</v>
+        <v>-1.477464215653175</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.263281389886133</v>
+        <v>2.264669475570091</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.775505357111596</v>
+        <v>-7.882038891707102</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.05349577902726921</v>
+        <v>0.0108823651890666</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.479777691793105</v>
+        <v>-1.477464215653175</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.276187731109792</v>
+        <v>2.27757581679375</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.881095346884701</v>
+        <v>-7.987628881480207</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1167161464811914</v>
+        <v>-0.159329560319394</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.585367681566209</v>
+        <v>-1.583054205426279</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.084857807646711</v>
+        <v>2.086245893330669</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.899830249003298</v>
+        <v>-8.006363783598804</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.0756657654515438</v>
+        <v>-0.1182791792897464</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.585367681566209</v>
+        <v>-1.583054205426279</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.133402149523797</v>
+        <v>2.134790235207755</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.751890207595698</v>
+        <v>-7.858423742191205</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1363686715766717</v>
+        <v>-0.1789820854148743</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.565046765657652</v>
+        <v>-1.562733289517722</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.025715776380764</v>
+        <v>2.027103862064722</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.727661571206726</v>
+        <v>-7.834195105802232</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.135391203274561</v>
+        <v>-0.1780046171127632</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.54081812926868</v>
+        <v>-1.538504653128749</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.03153897196067</v>
+        <v>2.032927057644628</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.684113164436035</v>
+        <v>-7.790646699031542</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.124932452661378</v>
+        <v>-0.1675458664995801</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.54081812926868</v>
+        <v>-1.538504653128749</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.024578359865576</v>
+        <v>2.025966445549535</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963419</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.441964770982177</v>
+        <v>-7.548498305577684</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.01361074089869163</v>
+        <v>-0.05622415473689379</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.54081812926868</v>
+        <v>-1.538504653128749</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.03904071424672</v>
+        <v>2.040428799930678</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.378735399213829</v>
+        <v>-7.485268933809335</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.006213128267842816</v>
+        <v>-0.03640028557035979</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.54081812926868</v>
+        <v>-1.538504653128749</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.033572834705915</v>
+        <v>2.034960920389873</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.255444264396698</v>
+        <v>-7.361977798992204</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.05302767620527193</v>
+        <v>0.01041426236706977</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.417526994451549</v>
+        <v>-1.415213518311619</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.10504560960677</v>
+        <v>2.106433695290728</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.234295065493255</v>
+        <v>-7.340828600088761</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.06918833400397473</v>
+        <v>0.02657492016577212</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.396377795548106</v>
+        <v>-1.394064319408176</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.125436107186161</v>
+        <v>2.126824192870119</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.99052962350981</v>
+        <v>-7.097063158105317</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1624752191444032</v>
+        <v>0.1198618053062006</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.396377795548106</v>
+        <v>-1.394064319408176</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.121216815533211</v>
+        <v>2.122604901217169</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.726501556316551</v>
+        <v>-6.833035090912057</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2702107599417229</v>
+        <v>0.2275973461035203</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.194512396732152</v>
+        <v>-1.192198920592222</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.2444603687428</v>
+        <v>2.245848454426758</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749183</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.476651162367476</v>
+        <v>-6.583184696962983</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.362892992505055</v>
+        <v>0.3202795786668524</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.194512396732152</v>
+        <v>-1.192198920592222</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.237202443726502</v>
+        <v>2.23859052941046</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481496</v>
+        <v>3.835954411481494</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.300759069900044</v>
+        <v>-6.40729260449555</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4368489530126762</v>
+        <v>0.3942355391744741</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.194512396732152</v>
+        <v>-1.192198920592222</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.24080156724715</v>
+        <v>2.242189652931109</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862986</v>
+        <v>3.780930335862984</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.129312606877581</v>
+        <v>-6.235846141473087</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5187550442762157</v>
+        <v>0.4761416304380131</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.023065933709689</v>
+        <v>-1.020752457569759</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.356996951115182</v>
+        <v>2.35838503679914</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102781</v>
+        <v>3.773761647102779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.904279607208758</v>
+        <v>-6.010813141804264</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6077887217600417</v>
+        <v>0.5651753079218391</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7980329340408662</v>
+        <v>-0.795719457900936</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.491037228532773</v>
+        <v>2.492425314216731</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353072</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.689645229572351</v>
+        <v>-5.796178764167857</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6983372738689217</v>
+        <v>0.6557238600307191</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5833985564044594</v>
+        <v>-0.5810850802645292</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.624512656168934</v>
+        <v>2.625900741852892</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544781</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.596645188366453</v>
+        <v>-5.703178722961959</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7167315491350768</v>
+        <v>0.6741181352968741</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5833985564044594</v>
+        <v>-0.5810850802645292</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.60570691495273</v>
+        <v>2.607095000636688</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712293</v>
+        <v>3.797691308712291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.356214691561592</v>
+        <v>-5.462748226157099</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8146468244818981</v>
+        <v>0.7720334106436955</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.3429680595995991</v>
+        <v>-0.3406545834596689</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.751708289660523</v>
+        <v>2.753096375344481</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837684</v>
+        <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.283972123390398</v>
+        <v>-5.390505657985904</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8474731655851961</v>
+        <v>0.8048597517469935</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.3429680595995991</v>
+        <v>-0.3406545834596689</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.755637603495344</v>
+        <v>2.757025689179302</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349966</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.168032273765212</v>
+        <v>-5.274565808360719</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8945276893526102</v>
+        <v>0.851914275514408</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.2661463285834752</v>
+        <v>-0.263832852443545</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.802409226022358</v>
+        <v>2.803797311706316</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861305097234</v>
+        <v>3.848613050972338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.92537668534205</v>
+        <v>-5.031910219937556</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9885879959418689</v>
+        <v>0.9459745821036663</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.2661463285834752</v>
+        <v>-0.263832852443545</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.799407297242351</v>
+        <v>2.800795382926309</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145939</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.705355887305039</v>
+        <v>-4.811889421900545</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.078175352167287</v>
+        <v>1.035561938329085</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.124926483515495</v>
+        <v>-0.1226130073755648</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.885718241293754</v>
+        <v>2.887106326977712</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327095200995</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.572488198241762</v>
+        <v>-4.679021732837268</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.147216610594422</v>
+        <v>1.104603196756219</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.124926483515495</v>
+        <v>-0.1226130073755648</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.901612424095577</v>
+        <v>2.903000509779535</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966257</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.412973094722392</v>
+        <v>-4.519506629317898</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.212168496442471</v>
+        <v>1.169555082604269</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.03458862000387497</v>
+        <v>0.03690209614380513</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.998467330647501</v>
+        <v>2.999855416331459</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046995</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.268300949622654</v>
+        <v>-4.374834484218161</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.280125457043806</v>
+        <v>1.237512043205604</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.1792607651036124</v>
+        <v>0.1815742412435425</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.095358720268783</v>
+        <v>3.096746805952741</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412103</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.328175776980347</v>
+        <v>-4.434709311575853</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.242213017502155</v>
+        <v>1.199599603663953</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1193859377459203</v>
+        <v>0.1216994138858504</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.045471315255594</v>
+        <v>3.046859400939552</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144514</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.241376279201338</v>
+        <v>-4.347909813796845</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.299333309936325</v>
+        <v>1.256719896098122</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1193859377459203</v>
+        <v>0.1216994138858504</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.06787180857816</v>
+        <v>3.069259894262118</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.72914282290069</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.243845985663144</v>
+        <v>-4.350379520258651</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.298417828725014</v>
+        <v>1.255804414886812</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1169162312841141</v>
+        <v>0.1192297074240443</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.066462386074488</v>
+        <v>3.067850471758446</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473597</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.312216171987155</v>
+        <v>-4.418749706582661</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.282076676670112</v>
+        <v>1.23946326283191</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.126191930320329</v>
+        <v>0.1285054064602592</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.083034727970919</v>
+        <v>3.084422813654877</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978366</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.190799742360678</v>
+        <v>-4.297333276956184</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.321079957152594</v>
+        <v>1.278466543314392</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.126191930320329</v>
+        <v>0.1285054064602592</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.07347143660281</v>
+        <v>3.074859522286769</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.7109031558877</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.221792901689383</v>
+        <v>-4.32832643628489</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.133392258461499</v>
+        <v>1.090778844623296</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.126191930320329</v>
+        <v>0.1285054064602592</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.898181001643197</v>
+        <v>2.899569087327155</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.746038950675898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.046318641896914</v>
+        <v>-4.15285217649242</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.208149194370274</v>
+        <v>1.165535780532072</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.126191930320329</v>
+        <v>0.1285054064602592</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.902748233634985</v>
+        <v>2.904136319318943</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.157254894538163</v>
+        <v>-4.263788429133669</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.139516722074982</v>
+        <v>1.096903308236779</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.126191930320329</v>
+        <v>0.1285054064602592</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.878490262396192</v>
+        <v>2.87987834808015</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.773206721581288</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.360281472081396</v>
+        <v>-4.466815006676902</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.061437476277594</v>
+        <v>1.018824062439392</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.07683464722290434</v>
+        <v>-0.07452117108297418</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.759805701090158</v>
+        <v>2.761193786774116</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734159</v>
+        <v>3.784340376734157</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.202355873146103</v>
+        <v>-4.308889407741609</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.134780102283844</v>
+        <v>1.092166688445641</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.07683464722290434</v>
+        <v>-0.07452117108297418</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.76997808752229</v>
+        <v>2.771366173206248</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212295</v>
+        <v>3.786946382212293</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.116112410119725</v>
+        <v>-4.222645944715231</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.164223758068255</v>
+        <v>1.121610344230053</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.07683464722290434</v>
+        <v>-0.07452117108297418</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.76492435809615</v>
+        <v>2.766312443780108</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786043</v>
+        <v>3.752023923786041</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.117295494770786</v>
+        <v>-4.223829029366293</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.155526299652356</v>
+        <v>1.112912885814154</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.08247769568941588</v>
+        <v>-0.08016421954948572</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.753314304460769</v>
+        <v>2.754702390144727</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.994167787776703</v>
+        <v>-4.10070132237221</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.205329255483091</v>
+        <v>1.162715841644888</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.08247769568941588</v>
+        <v>-0.08016421954948572</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.75386617749387</v>
+        <v>2.755254263177828</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.901357306325844</v>
+        <v>-4.00789084092135</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.1717261399548</v>
+        <v>1.129112726116598</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.01033278576144347</v>
+        <v>0.01264626190137363</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.738825158255751</v>
+        <v>2.74021324393971</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.852794254104814</v>
+        <v>-3.95932778870032</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.193024836767813</v>
+        <v>1.150411422929611</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.05889583798247366</v>
+        <v>0.06120931412240382</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.769836465512971</v>
+        <v>2.771224551196929</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.839719946161641</v>
+        <v>-3.84665657046407</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.193330268456805</v>
+        <v>1.190555618735834</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.07197014592564666</v>
+        <v>0.173880532358654</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.772756758790597</v>
+        <v>2.833902990650402</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.727342944978969</v>
+        <v>-3.734279569281397</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.243772364760542</v>
+        <v>1.24099771503957</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.07197014592564666</v>
+        <v>0.173880532358654</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.778248054621264</v>
+        <v>2.839394286481069</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.689594264968859</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.925577513865699</v>
+        <v>-3.932514138168127</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.175975738974389</v>
+        <v>1.173201089253417</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1262644229610839</v>
+        <v>-0.02435403652807655</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.670804515057765</v>
+        <v>2.73195074691757</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175319</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.008578794890978</v>
+        <v>-4.015515419193406</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9811309465649303</v>
+        <v>0.9783562968439588</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1448353074882577</v>
+        <v>-0.04292492105525031</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.498017704342114</v>
+        <v>2.559163936201919</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.682712735199266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.849384522834402</v>
+        <v>-3.85632114713683</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.164958316106766</v>
+        <v>1.162183666385795</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1448353074882577</v>
+        <v>-0.04292492105525031</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.61816736506132</v>
+        <v>2.679313596921125</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660767</v>
+        <v>3.733008865660765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.935983105815505</v>
+        <v>-3.942919730117933</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.144831909016648</v>
+        <v>1.142057259295677</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1448353074882577</v>
+        <v>-0.04292492105525031</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.632680391163643</v>
+        <v>2.693826623023448</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383421</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.897599443257354</v>
+        <v>-3.904536067559782</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.157604815382277</v>
+        <v>1.154830165661306</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1064516449301065</v>
+        <v>-0.004541258497099132</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.653130030040902</v>
+        <v>2.714276261900707</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002483</v>
+        <v>3.751143622002481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.720483113222187</v>
+        <v>-3.727419737524615</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.225180376241646</v>
+        <v>1.222405726520674</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1064516449301065</v>
+        <v>-0.004541258497099132</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.649859058886204</v>
+        <v>2.711005290746009</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263901</v>
+        <v>3.741324873263899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.690780989245894</v>
+        <v>-3.697717613548322</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.237744617594076</v>
+        <v>1.234969967873105</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1109217701454199</v>
+        <v>-0.009011383712412502</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.647860375518929</v>
+        <v>2.709006607378734</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481235</v>
+        <v>3.750725801481233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.511405568007126</v>
+        <v>-3.518342192309554</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.303281761395998</v>
+        <v>1.300507111675026</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.0458549880252988</v>
+        <v>0.1477653744583062</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.735713405727775</v>
+        <v>2.796859637587579</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71698814345223</v>
+        <v>3.716988143452228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.556419781527732</v>
+        <v>-3.56335640583016</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.266083531319345</v>
+        <v>1.263308881598374</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.0155060927106942</v>
+        <v>0.1174164791437016</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.698311523870602</v>
+        <v>2.759457755730407</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979537</v>
+        <v>3.737023032979535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.823424291800167</v>
+        <v>-3.830360916102595</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.164973289549317</v>
+        <v>1.162198639828345</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1788569453322544</v>
+        <v>-0.07694655889924701</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.587385263383779</v>
+        <v>2.648531495243583</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230806</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.112211512259083</v>
+        <v>-4.119148136561511</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.048662323262252</v>
+        <v>1.045887673541281</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2799430654312547</v>
+        <v>-0.1780326789982474</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.52593751322088</v>
+        <v>2.587083745080684</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285452</v>
+        <v>3.70556808628545</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.07973592608831</v>
+        <v>-4.086672550390738</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.059252519284878</v>
+        <v>1.056477869563906</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2799430654312547</v>
+        <v>-0.1780326789982474</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.523537474775197</v>
+        <v>2.584683706635001</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095068678481</v>
+        <v>3.709506867848098</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.060697798381013</v>
+        <v>-4.067634422683441</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.063392489576041</v>
+        <v>1.06061783985507</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3381266767624493</v>
+        <v>-0.2362162903294419</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.485152027184724</v>
+        <v>2.546298259044529</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601247</v>
+        <v>3.84519413284728</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.077443663637388</v>
+        <v>-4.084380287939816</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.234276012412172</v>
+        <v>1.2315013626912</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3381266767624493</v>
+        <v>-0.2362162903294419</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.662733896123405</v>
+        <v>2.72388012798321</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.842786006525358</v>
+        <v>3.589815659351027</v>
       </c>
       <c r="C1964" t="n">
-        <v>3.054078350717629</v>
+        <v>2.866538266697957</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.077443663637388</v>
+        <v>-4.084380287939816</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.234276012412172</v>
+        <v>1.2315013626912</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3381266767624493</v>
+        <v>-0.2362162903294419</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.047142147703997</v>
+        <v>2.859602063684325</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240514.xlsx
+++ b/tame_output/ON/bt/strategyON_20240514.xlsx
@@ -605,12 +605,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.8%</t>
+          <t>113.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.2%</t>
+          <t>132.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-706.6%</t>
+          <t>-707.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.5%</t>
+          <t>-53.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.1%</t>
+          <t>444.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-570.0%</t>
+          <t>-586.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.0%</t>
+          <t>-283.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.1%</t>
+          <t>-42.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-253.1%</t>
+          <t>-259.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-33.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-462.6%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-183.3%</t>
+          <t>-247.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-247.6%</t>
+          <t>-257.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-29.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7393852932076951</v>
+        <v>-0.7431557962942377</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.825218220729901</v>
+        <v>2.823710019495283</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.946951077599307</v>
+        <v>-0.9507215806858496</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.740016703092496</v>
+        <v>2.738508501857879</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.364705101146144</v>
+        <v>-1.368475604232686</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.570841985178824</v>
+        <v>2.569333783944208</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.586327034704262</v>
+        <v>-1.590097537790804</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.482059428354499</v>
+        <v>2.480551227119882</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9143710060726489</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.794331093057339</v>
+        <v>-1.798101596143881</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.403749949567194</v>
+        <v>2.402241748332576</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9143710060726489</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.005743513945314</v>
+        <v>-2.009514017031856</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.314266437549992</v>
+        <v>2.312758236315375</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7029585851846738</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.344901891533836</v>
+        <v>-2.348672394620378</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.171687385821032</v>
+        <v>2.170179184586415</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3638002075961517</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.553392672985521</v>
+        <v>-2.557163176072063</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.108629362979126</v>
+        <v>2.10712116174451</v>
       </c>
       <c r="F1852" t="n">
         <v>0.1553094261444673</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.046717544520699</v>
+        <v>-3.050488047607241</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.919398164773623</v>
+        <v>1.917889963539007</v>
       </c>
       <c r="F1853" t="n">
         <v>0.05032331190484857</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382331</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.539102572544796</v>
+        <v>-3.542873075631338</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.723550545607717</v>
+        <v>1.7220423443731</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.4420617161192482</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.924282963474868</v>
+        <v>-3.92805346656141</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.568020928048551</v>
+        <v>1.566512726813934</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.4420617161192482</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.267965736701531</v>
+        <v>-4.271736239788073</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.432316942212502</v>
+        <v>1.430808740977886</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.5499677681464663</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.474477513588552</v>
+        <v>-4.478248016675094</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.345818290113952</v>
+        <v>1.344310088879335</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.7564795450334878</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.783711616584603</v>
+        <v>-4.787482119671145</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.223897575615791</v>
+        <v>1.222389374381174</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.7564795450334878</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.215517409734391</v>
+        <v>-5.219287912820932</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.03750814582328</v>
+        <v>1.035999944588664</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8928970414747548</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310983</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.450211403866943</v>
+        <v>-5.453981906953485</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9319153231723503</v>
+        <v>0.9304071219377335</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8865607742454996</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.785874051097395</v>
+        <v>-5.789644554183937</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7962308559361344</v>
+        <v>0.7947226547015176</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8865607742454996</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.149500295997709</v>
+        <v>-6.15327079908425</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6572679182102505</v>
+        <v>0.6557597169756337</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9847824111126254</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.514627678636455</v>
+        <v>-6.518398181722997</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5104714801605832</v>
+        <v>0.5089632789259664</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.281093195411638</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.923216455817133</v>
+        <v>-6.926986958903676</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3457975133030708</v>
+        <v>0.344289312068454</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.689681972592316</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.336198939958227</v>
+        <v>-7.33996944304477</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1757899521180941</v>
+        <v>0.1742817508834769</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.689681972592316</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.752590814245225</v>
+        <v>-7.756361317331767</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.007227253012172419</v>
+        <v>0.005719051777555606</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.689681972592316</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.129267824775068</v>
+        <v>-8.133038327861611</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1331848605310859</v>
+        <v>-0.1346930617657032</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.689681972592316</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.475142646759878</v>
+        <v>-8.47891314984642</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2754352241793145</v>
+        <v>-0.2769434254139314</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.689681972592316</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.638722524944262</v>
+        <v>-8.642493028030804</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3424622553980674</v>
+        <v>-0.3439704566326842</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.689681972592316</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.93538386675446</v>
+        <v>-8.939154369841003</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4573478161929385</v>
+        <v>-0.4588560174275553</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.758425108326195</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.058628255969889</v>
+        <v>-9.062398759056432</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5106718764135132</v>
+        <v>-0.5121800776481304</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.758425108326195</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.441629644712521</v>
+        <v>-9.445400147799063</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6639745332321496</v>
+        <v>-0.6654827344667669</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.758425108326195</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.599028524925641</v>
+        <v>-9.602799028012184</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7243625693459679</v>
+        <v>-0.7258707705805851</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.915823988539316</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.958558847429643</v>
+        <v>-9.962329350516185</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8628243950495182</v>
+        <v>-0.8643325962841355</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.915823988539316</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.00890791088387</v>
+        <v>-10.01267841397041</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8750480004740298</v>
+        <v>-0.8765562017086466</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.966173051993538</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.22805687895806</v>
+        <v>-10.2318273820446</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9596658370819395</v>
+        <v>-0.9611740383165572</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.185322020067736</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.22436595400165</v>
+        <v>-10.22813645708819</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9581894670993756</v>
+        <v>-0.9596976683339924</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.185322020067736</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.42862412933152</v>
+        <v>-10.43239463241806</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.034379540112679</v>
+        <v>-1.035887741347295</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.312960964681725</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.64666190096269</v>
+        <v>-10.65043240404924</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.117112094280714</v>
+        <v>-1.118620295515331</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.487731732777624</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.57319206929524</v>
+        <v>-10.57696257238179</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.072352460120313</v>
+        <v>-1.07386066135493</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.414261901110175</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078599</v>
+        <v>3.4900556660786</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.74831648668179</v>
+        <v>-10.75208698976833</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.127847006327413</v>
+        <v>-1.12935520756203</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.589386318496719</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.98276858069628</v>
+        <v>-10.98653908378282</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.228847008834805</v>
+        <v>-1.230355210069422</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.589386318496719</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.27057242523352</v>
+        <v>-11.27434292832006</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.350640737423677</v>
+        <v>-1.352148938658294</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.877190163033957</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.32335858083384</v>
+        <v>-11.32712908392038</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.370639409825252</v>
+        <v>-1.372147611059868</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.972865649616354</v>
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.4920980657674</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.39328462384612</v>
+        <v>-11.55915800365665</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.395916098401048</v>
+        <v>-1.462265450325259</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.936139185152558</v>
+        <v>-3.034878346804777</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.400070664359613</v>
+        <v>1.340827167368281</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.34126910987731</v>
+        <v>-11.50714248968783</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.371119557127122</v>
+        <v>-1.437468909051332</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.936139185152558</v>
+        <v>-3.034878346804777</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.404061000046014</v>
+        <v>1.344817503054682</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.48294095160143</v>
+        <v>-11.64881433141195</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.429263520715512</v>
+        <v>-1.495612872639722</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.936139185152558</v>
+        <v>-3.034878346804777</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.402585773147272</v>
+        <v>1.343342276155941</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.43335010717659</v>
+        <v>-11.59922348698712</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.394373772780706</v>
+        <v>-1.460723124704916</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.886548340727725</v>
+        <v>-2.985287502379943</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.447393689967045</v>
+        <v>1.388150192975713</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.23419799993949</v>
+        <v>-11.40007137975002</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.32776406353255</v>
+        <v>-1.394113415456759</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.721225814777911</v>
+        <v>-2.81996497643013</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.53353607189025</v>
+        <v>1.474292574898918</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.00835284722008</v>
+        <v>-11.17422622703061</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.227846929408577</v>
+        <v>-1.294196281332786</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.679299139190748</v>
+        <v>-2.778038300842967</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.568271150278756</v>
+        <v>1.509027653287425</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.88377419088249</v>
+        <v>-11.04964757069302</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.176876322317481</v>
+        <v>-1.24322567424169</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.679299139190748</v>
+        <v>-2.778038300842967</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.569410294834815</v>
+        <v>1.510166797843484</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.93666947892678</v>
+        <v>-11.1025428587373</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.195400663373088</v>
+        <v>-1.261750015297298</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.674343793102302</v>
+        <v>-2.77308295475452</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.575017276649991</v>
+        <v>1.515773779658659</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081567</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.65276074799803</v>
+        <v>-10.81863412780855</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.076103466762952</v>
+        <v>-1.142452818687161</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.674343793102302</v>
+        <v>-2.77308295475452</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.580750980888627</v>
+        <v>1.521507483897296</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.58139435538838</v>
+        <v>-10.74726773519891</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.057294172112958</v>
+        <v>-1.123643524037168</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.602977400492654</v>
+        <v>-2.701716562144873</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.613833554060551</v>
+        <v>1.554590057069219</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.31755748818431</v>
+        <v>-10.48343086799484</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9616429065442378</v>
+        <v>-1.027992258468447</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.602977400492654</v>
+        <v>-2.701716562144873</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.603950072747643</v>
+        <v>1.544706575756312</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906226</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.05031568731592</v>
+        <v>-10.21618906712644</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8565807466962521</v>
+        <v>-0.9229300986204616</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.602977400492654</v>
+        <v>-2.701716562144873</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.602115512248269</v>
+        <v>1.542872015256938</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.952408648639425</v>
+        <v>-10.11828202844995</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8177182461991168</v>
+        <v>-0.8840675981233264</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.534991650632097</v>
+        <v>-2.633730812284316</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.642606647191142</v>
+        <v>1.583363150199811</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.928455107663467</v>
+        <v>-10.09432848747399</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8074683236632403</v>
+        <v>-0.8738176755874494</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.51103810965614</v>
+        <v>-2.609777271308359</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.65764727792221</v>
+        <v>1.598403780930879</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.66439516934067</v>
+        <v>-9.830268549151194</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7151046644958736</v>
+        <v>-0.7814540164200832</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.246978171333344</v>
+        <v>-2.345717332985563</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.802822924754136</v>
+        <v>1.743579427762805</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309725</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.957315545835833</v>
+        <v>-9.123188925646357</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4350598487542396</v>
+        <v>-0.5014092006784492</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.246978171333344</v>
+        <v>-2.345717332985563</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.800035891093835</v>
+        <v>1.740792394102504</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.83937087185873</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.917131247469642</v>
+        <v>-9.083004627280166</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4186425055199221</v>
+        <v>-0.4849918574441316</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.206793872967153</v>
+        <v>-2.305533034619372</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.824490094001391</v>
+        <v>1.765246597010059</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096474</v>
+        <v>3.856158176096476</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.837061451931838</v>
+        <v>-9.002934831742362</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3872477660840432</v>
+        <v>-0.4535971180082528</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.126724077429349</v>
+        <v>-2.225463239081568</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.87189879254483</v>
+        <v>1.812655295553499</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.603580229702239</v>
+        <v>-8.769453609512762</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2859308483543512</v>
+        <v>-0.3522802002785608</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.89324285519975</v>
+        <v>-1.991982016851969</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.019911954720442</v>
+        <v>1.960668457729111</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.453913838694724</v>
+        <v>-8.619787218505248</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2289565022643045</v>
+        <v>-0.2953058541885141</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.800339363957215</v>
+        <v>-1.899078525609433</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.072761839153004</v>
+        <v>2.013518342161673</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.321638365063837</v>
+        <v>-8.487511744874361</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1806788260649226</v>
+        <v>-0.2470281779891321</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.668063890326328</v>
+        <v>-1.766803051978547</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.147494610078563</v>
+        <v>2.088251113087232</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.131038690390683</v>
+        <v>-8.296912070201207</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1016238955080246</v>
+        <v>-0.1679732474322342</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.477464215653175</v>
+        <v>-1.576203377305394</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.264669475570091</v>
+        <v>2.20542597857876</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.882038891707102</v>
+        <v>-8.047912271517626</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.0108823651890666</v>
+        <v>-0.05546698673514294</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.477464215653175</v>
+        <v>-1.576203377305394</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.27757581679375</v>
+        <v>2.218332319802419</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.987628881480207</v>
+        <v>-8.153502261290731</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.159329560319394</v>
+        <v>-0.2256789122436036</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.583054205426279</v>
+        <v>-1.681793367078498</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.086245893330669</v>
+        <v>2.027002396339338</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.006363783598804</v>
+        <v>-8.172237163409328</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1182791792897464</v>
+        <v>-0.1846285312139559</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.583054205426279</v>
+        <v>-1.681793367078498</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.134790235207755</v>
+        <v>2.075546738216424</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.858423742191205</v>
+        <v>-8.024297122001729</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1789820854148743</v>
+        <v>-0.2453314373390838</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.562733289517722</v>
+        <v>-1.661472451169941</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.027103862064722</v>
+        <v>1.967860365073391</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.834195105802232</v>
+        <v>-8.000068485612756</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1780046171127632</v>
+        <v>-0.2443539690369727</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.538504653128749</v>
+        <v>-1.637243814780968</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.032927057644628</v>
+        <v>1.973683560653296</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.790646699031542</v>
+        <v>-7.956520078842066</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1675458664995801</v>
+        <v>-0.2338952184237897</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.538504653128749</v>
+        <v>-1.637243814780968</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.025966445549535</v>
+        <v>1.966722948558203</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.548498305577684</v>
+        <v>-7.714371685388207</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.05622415473689379</v>
+        <v>-0.1225735066611033</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.538504653128749</v>
+        <v>-1.637243814780968</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.040428799930678</v>
+        <v>1.981185302939346</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.485268933809335</v>
+        <v>-7.651142313619859</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.03640028557035979</v>
+        <v>-0.1027496374945693</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.538504653128749</v>
+        <v>-1.637243814780968</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.034960920389873</v>
+        <v>1.975717423398541</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.361977798992204</v>
+        <v>-7.527851178802728</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.01041426236706977</v>
+        <v>-0.05593508955713977</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.415213518311619</v>
+        <v>-1.513952679963838</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.106433695290728</v>
+        <v>2.047190198299396</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.340828600088761</v>
+        <v>-7.506701979899285</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.02657492016577212</v>
+        <v>-0.03977443175843742</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.394064319408176</v>
+        <v>-1.492803481060395</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.126824192870119</v>
+        <v>2.067580695878787</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788092</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.097063158105317</v>
+        <v>-7.262936537915841</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1198618053062006</v>
+        <v>0.05351245338199107</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.394064319408176</v>
+        <v>-1.492803481060395</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.122604901217169</v>
+        <v>2.063361404225838</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527523</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.833035090912057</v>
+        <v>-6.998908470722581</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2275973461035203</v>
+        <v>0.1612479941793108</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.192198920592222</v>
+        <v>-1.290938082244441</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.245848454426758</v>
+        <v>2.186604957435426</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.826351398749183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.583184696962983</v>
+        <v>-6.749058076773506</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3202795786668524</v>
+        <v>0.2539302267426429</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.192198920592222</v>
+        <v>-1.290938082244441</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.23859052941046</v>
+        <v>2.179347032419129</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481494</v>
+        <v>3.835954411481496</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.40729260449555</v>
+        <v>-6.573165984306074</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3942355391744741</v>
+        <v>0.3278861872502645</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.192198920592222</v>
+        <v>-1.290938082244441</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.242189652931109</v>
+        <v>2.182946155939777</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862984</v>
+        <v>3.780930335862986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.235846141473087</v>
+        <v>-6.401719521283611</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4761416304380131</v>
+        <v>0.4097922785138035</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.020752457569759</v>
+        <v>-1.119491619221978</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.35838503679914</v>
+        <v>2.299141539807809</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102779</v>
+        <v>3.773761647102781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.010813141804264</v>
+        <v>-6.176686521614788</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5651753079218391</v>
+        <v>0.4988259559976296</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.795719457900936</v>
+        <v>-0.8944586195531549</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.492425314216731</v>
+        <v>2.4331818172254</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.796178764167857</v>
+        <v>-5.962052143978381</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6557238600307191</v>
+        <v>0.5893745081065096</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.5810850802645292</v>
+        <v>-0.6798242419167481</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.625900741852892</v>
+        <v>2.566657244861561</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.703178722961959</v>
+        <v>-5.869052102772483</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6741181352968741</v>
+        <v>0.6077687833726646</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.5810850802645292</v>
+        <v>-0.6798242419167481</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.607095000636688</v>
+        <v>2.547851503645357</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712291</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.462748226157099</v>
+        <v>-5.628621605967623</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7720334106436955</v>
+        <v>0.7056840587194859</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.3406545834596689</v>
+        <v>-0.4393937451118878</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.753096375344481</v>
+        <v>2.69385287835315</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837682</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.390505657985904</v>
+        <v>-5.556379037796428</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8048597517469935</v>
+        <v>0.738510399822784</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.3406545834596689</v>
+        <v>-0.4393937451118878</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.757025689179302</v>
+        <v>2.69778219218797</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.274565808360719</v>
+        <v>-5.440439188171243</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.851914275514408</v>
+        <v>0.7855649235901985</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.263832852443545</v>
+        <v>-0.3625720140957639</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.803797311706316</v>
+        <v>2.744553814714985</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972338</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.031910219937556</v>
+        <v>-5.19778359974808</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9459745821036663</v>
+        <v>0.8796252301794567</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.263832852443545</v>
+        <v>-0.3625720140957639</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.800795382926309</v>
+        <v>2.741551885934978</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.811889421900545</v>
+        <v>-4.977762801711069</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.035561938329085</v>
+        <v>0.9692125864048753</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.1226130073755648</v>
+        <v>-0.2213521690277837</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.887106326977712</v>
+        <v>2.82786282998638</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.84327095200995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.679021732837268</v>
+        <v>-4.844895112647792</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.104603196756219</v>
+        <v>1.03825384483201</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.1226130073755648</v>
+        <v>-0.2213521690277837</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.903000509779535</v>
+        <v>2.843757012788203</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.519506629317898</v>
+        <v>-4.685380009128422</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.169555082604269</v>
+        <v>1.103205730680059</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.03690209614380513</v>
+        <v>-0.06183706550841372</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.999855416331459</v>
+        <v>2.940611919340127</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.374834484218161</v>
+        <v>-4.540707864028684</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.237512043205604</v>
+        <v>1.171162691281394</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.1815742412435425</v>
+        <v>0.08283507959132369</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.096746805952741</v>
+        <v>3.03750330896141</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.434709311575853</v>
+        <v>-4.600582691386377</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.199599603663953</v>
+        <v>1.133250251739743</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.1216994138858504</v>
+        <v>0.02296025223363157</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.046859400939552</v>
+        <v>2.98761590394822</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.347909813796845</v>
+        <v>-4.513783193607368</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.256719896098122</v>
+        <v>1.190370544173913</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.1216994138858504</v>
+        <v>0.02296025223363157</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.069259894262118</v>
+        <v>3.010016397270786</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914282290069</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.350379520258651</v>
+        <v>-4.516252900069174</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.255804414886812</v>
+        <v>1.189455062962602</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.1192297074240443</v>
+        <v>0.02049054577182541</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.067850471758446</v>
+        <v>3.008606974767115</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473597</v>
+        <v>3.743216620473598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.418749706582661</v>
+        <v>-4.584623086393185</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.23946326283191</v>
+        <v>1.1731139109077</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.1285054064602592</v>
+        <v>0.02976624480804035</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.084422813654877</v>
+        <v>3.025179316663546</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978366</v>
+        <v>3.714175563978367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.297333276956184</v>
+        <v>-4.463206656766708</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.278466543314392</v>
+        <v>1.212117191390182</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.1285054064602592</v>
+        <v>0.02976624480804035</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.074859522286769</v>
+        <v>3.015616025295437</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109031558877</v>
+        <v>3.710903155887701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.32832643628489</v>
+        <v>-4.494199816095414</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.090778844623296</v>
+        <v>1.024429492699087</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.1285054064602592</v>
+        <v>0.02976624480804035</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.899569087327155</v>
+        <v>2.840325590335824</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675898</v>
+        <v>3.746038950675899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.15285217649242</v>
+        <v>-4.318725556302944</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.165535780532072</v>
+        <v>1.099186428607863</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.1285054064602592</v>
+        <v>0.02976624480804035</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.904136319318943</v>
+        <v>2.844892822327612</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695443</v>
+        <v>3.765020747695444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.263788429133669</v>
+        <v>-4.429661808944193</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.096903308236779</v>
+        <v>1.03055395631257</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.1285054064602592</v>
+        <v>0.02976624480804035</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.87987834808015</v>
+        <v>2.820634851088819</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581288</v>
+        <v>3.773206721581289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.466815006676902</v>
+        <v>-4.632688386487426</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.018824062439392</v>
+        <v>0.9524747105151823</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.07452117108297418</v>
+        <v>-0.173260332735193</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.761193786774116</v>
+        <v>2.701950289782785</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734157</v>
+        <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.308889407741609</v>
+        <v>-4.474762787552133</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.092166688445641</v>
+        <v>1.025817336521432</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.07452117108297418</v>
+        <v>-0.173260332735193</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.771366173206248</v>
+        <v>2.712122676214917</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212293</v>
+        <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.222645944715231</v>
+        <v>-4.388519324525755</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.121610344230053</v>
+        <v>1.055260992305843</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.07452117108297418</v>
+        <v>-0.173260332735193</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.766312443780108</v>
+        <v>2.707068946788777</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786041</v>
+        <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.223829029366293</v>
+        <v>-4.389702409176817</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.112912885814154</v>
+        <v>1.046563533889944</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.08016421954948572</v>
+        <v>-0.1789033812017046</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.754702390144727</v>
+        <v>2.695458893153396</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.10070132237221</v>
+        <v>-4.266574702182734</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.162715841644888</v>
+        <v>1.096366489720679</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.08016421954948572</v>
+        <v>-0.1789033812017046</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.755254263177828</v>
+        <v>2.696010766186497</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.00789084092135</v>
+        <v>-4.173764220731874</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.129112726116598</v>
+        <v>1.062763374192389</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.01264626190137363</v>
+        <v>-0.08609289975084522</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.74021324393971</v>
+        <v>2.680969746948378</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.95932778870032</v>
+        <v>-4.125201168510844</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.150411422929611</v>
+        <v>1.084062071005401</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.06120931412240382</v>
+        <v>-0.03752984752981503</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.771224551196929</v>
+        <v>2.711981054205598</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942736</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.84665657046407</v>
+        <v>-4.012529950274594</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.190555618735834</v>
+        <v>1.124206266811624</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.173880532358654</v>
+        <v>0.07514137070643517</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.833902990650402</v>
+        <v>2.774659493659071</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.734279569281397</v>
+        <v>-3.900152949091921</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.24099771503957</v>
+        <v>1.174648363115361</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.173880532358654</v>
+        <v>0.07514137070643517</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.839394286481069</v>
+        <v>2.780150789489738</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968859</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.932514138168127</v>
+        <v>-4.098387517978652</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.173201089253417</v>
+        <v>1.106851737329207</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.02435403652807655</v>
+        <v>-0.1230931981802954</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.73195074691757</v>
+        <v>2.672707249926238</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175319</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.015515419193406</v>
+        <v>-4.181388799003931</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9783562968439588</v>
+        <v>0.9120069449197492</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.04292492105525031</v>
+        <v>-0.1416640827074692</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.559163936201919</v>
+        <v>2.499920439210587</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199266</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.85632114713683</v>
+        <v>-4.022194526947354</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.162183666385795</v>
+        <v>1.095834314461585</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.04292492105525031</v>
+        <v>-0.1416640827074692</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.679313596921125</v>
+        <v>2.620070099929793</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660765</v>
+        <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.942919730117933</v>
+        <v>-4.108793109928457</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.142057259295677</v>
+        <v>1.075707907371467</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.04292492105525031</v>
+        <v>-0.1416640827074692</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.693826623023448</v>
+        <v>2.634583126032116</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383421</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.904536067559782</v>
+        <v>-4.070409447370306</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.154830165661306</v>
+        <v>1.088480813737096</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.004541258497099132</v>
+        <v>-0.103280420149318</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.714276261900707</v>
+        <v>2.655032764909376</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002481</v>
+        <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.727419737524615</v>
+        <v>-3.89329311733514</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.222405726520674</v>
+        <v>1.156056374596465</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.004541258497099132</v>
+        <v>-0.103280420149318</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.711005290746009</v>
+        <v>2.651761793754678</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263899</v>
+        <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.697717613548322</v>
+        <v>-3.863590993358846</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.234969967873105</v>
+        <v>1.168620615948895</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.009011383712412502</v>
+        <v>-0.1077505453646314</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.709006607378734</v>
+        <v>2.649763110387402</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481233</v>
+        <v>3.750725801481235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.518342192309554</v>
+        <v>-3.684215572120078</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.300507111675026</v>
+        <v>1.234157759750817</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1477653744583062</v>
+        <v>0.04902621280608732</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.796859637587579</v>
+        <v>2.737616140596248</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452228</v>
+        <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.56335640583016</v>
+        <v>-3.729229785640685</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.263308881598374</v>
+        <v>1.196959529674164</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1174164791437016</v>
+        <v>0.01867731749148271</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.759457755730407</v>
+        <v>2.700214258739075</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979535</v>
+        <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.830360916102595</v>
+        <v>-3.99623429591312</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.162198639828345</v>
+        <v>1.095849287904135</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.07694655889924701</v>
+        <v>-0.1756857205514659</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.648531495243583</v>
+        <v>2.589287998252252</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.119148136561511</v>
+        <v>-4.285021516372035</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.045887673541281</v>
+        <v>0.979538321617071</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.1780326789982474</v>
+        <v>-0.2767718406504662</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.587083745080684</v>
+        <v>2.527840248089353</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70556808628545</v>
+        <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.086672550390738</v>
+        <v>-4.252545930201263</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.056477869563906</v>
+        <v>0.9901285176396966</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.1780326789982474</v>
+        <v>-0.2767718406504662</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.584683706635001</v>
+        <v>2.52544020964367</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848098</v>
+        <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.067634422683441</v>
+        <v>-4.233507802493966</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.06061783985507</v>
+        <v>0.9942684879308603</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2362162903294419</v>
+        <v>-0.3349554519816608</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.546298259044529</v>
+        <v>2.487054762053198</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.84519413284728</v>
+        <v>3.731060897601248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.084380287939816</v>
+        <v>-4.250253667750341</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.2315013626912</v>
+        <v>1.165152010766991</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2362162903294419</v>
+        <v>-0.3349554519816608</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.72388012798321</v>
+        <v>2.664636630991879</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,19 +46717,19 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.589815659351027</v>
+        <v>3.558875345260864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866538266697957</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.084380287939816</v>
+        <v>-4.250253667750341</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.2315013626912</v>
+        <v>1.165152010766991</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2362162903294419</v>
+        <v>-0.3349554519816608</v>
       </c>
       <c r="G1964" t="n">
         <v>2.859602063684325</v>

--- a/tame_output/ON/bt/strategyON_20240514.xlsx
+++ b/tame_output/ON/bt/strategyON_20240514.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-21.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-25.0%</t>
+          <t>-25.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.2%</t>
+          <t>112.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.9%</t>
+          <t>132.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-707.0%</t>
+          <t>-697.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.1%</t>
+          <t>-52.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-74.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.3%</t>
+          <t>444.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-586.6%</t>
+          <t>-577.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.2%</t>
+          <t>-279.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.6%</t>
+          <t>-42.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-28.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-259.7%</t>
+          <t>-256.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-29.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-257.5%</t>
+          <t>-264.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.1%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-160.1%</t>
+          <t>-184.3%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7431557962942377</v>
+        <v>-0.6452155037515721</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.823710019495283</v>
+        <v>2.86288613651235</v>
       </c>
       <c r="F1845" t="n">
         <v>1.577216947698467</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201491</v>
+        <v>3.295507330201492</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.9507215806858496</v>
+        <v>-0.852781288143184</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.738508501857879</v>
+        <v>2.777684618874945</v>
       </c>
       <c r="F1846" t="n">
         <v>1.369651163306855</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.368475604232686</v>
+        <v>-1.270535311690021</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.569333783944208</v>
+        <v>2.608509900961274</v>
       </c>
       <c r="F1847" t="n">
         <v>0.9518971397600179</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.27116857953743</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.590097537790804</v>
+        <v>-1.492157245248138</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.480551227119882</v>
+        <v>2.519727344136949</v>
       </c>
       <c r="F1848" t="n">
         <v>0.9143710060726489</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.798101596143881</v>
+        <v>-1.700161303601216</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.402241748332576</v>
+        <v>2.441417865349643</v>
       </c>
       <c r="F1849" t="n">
         <v>0.9143710060726489</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-2.009514017031856</v>
+        <v>-1.911573724489191</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.312758236315375</v>
+        <v>2.351934353332441</v>
       </c>
       <c r="F1850" t="n">
         <v>0.7029585851846738</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.348672394620378</v>
+        <v>-2.250732102077713</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.170179184586415</v>
+        <v>2.209355301603481</v>
       </c>
       <c r="F1851" t="n">
         <v>0.3638002075961517</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.557163176072063</v>
+        <v>-2.459222883529397</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.10712116174451</v>
+        <v>2.146297278761576</v>
       </c>
       <c r="F1852" t="n">
         <v>0.1553094261444673</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-3.050488047607241</v>
+        <v>-2.952547755064575</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.917889963539007</v>
+        <v>1.957066080556073</v>
       </c>
       <c r="F1853" t="n">
         <v>0.05032331190484857</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.542873075631338</v>
+        <v>-3.444932783088672</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.7220423443731</v>
+        <v>1.761218461390166</v>
       </c>
       <c r="F1854" t="n">
         <v>-0.4420617161192482</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.92805346656141</v>
+        <v>-3.830113174018745</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.566512726813934</v>
+        <v>1.605688843831001</v>
       </c>
       <c r="F1855" t="n">
         <v>-0.4420617161192482</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.271736239788073</v>
+        <v>-4.173795947245408</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.430808740977886</v>
+        <v>1.469984857994952</v>
       </c>
       <c r="F1856" t="n">
         <v>-0.5499677681464663</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.478248016675094</v>
+        <v>-4.380307724132429</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.344310088879335</v>
+        <v>1.383486205896401</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.7564795450334878</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.787482119671145</v>
+        <v>-4.68954182712848</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.222389374381174</v>
+        <v>1.26156549139824</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.7564795450334878</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.219287912820932</v>
+        <v>-5.121347620278267</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.035999944588664</v>
+        <v>1.07517606160573</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.8928970414747548</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.453981906953485</v>
+        <v>-5.356041614410819</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9304071219377335</v>
+        <v>0.9695832389547996</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.8865607742454996</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.789644554183937</v>
+        <v>-5.691704261641272</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.7947226547015176</v>
+        <v>0.8338987717185837</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.8865607742454996</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.15327079908425</v>
+        <v>-6.055330506541585</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6557597169756337</v>
+        <v>0.6949358339926999</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.9847824111126254</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.518398181722997</v>
+        <v>-6.420457889180332</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5089632789259664</v>
+        <v>0.5481393959430325</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.281093195411638</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.926986958903676</v>
+        <v>-6.829046666361011</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.344289312068454</v>
+        <v>0.3834654290855202</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.689681972592316</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.33996944304477</v>
+        <v>-7.242029150502105</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.1742817508834769</v>
+        <v>0.213457867900543</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.689681972592316</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.756361317331767</v>
+        <v>-7.658421024789102</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.005719051777555606</v>
+        <v>0.0448951687946213</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.689681972592316</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.133038327861611</v>
+        <v>-8.035098035318946</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.1346930617657032</v>
+        <v>-0.09551694474863703</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.689681972592316</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.47891314984642</v>
+        <v>-8.380972857303755</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2769434254139314</v>
+        <v>-0.2377673083968657</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.689681972592316</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.642493028030804</v>
+        <v>-8.544552735488139</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3439704566326842</v>
+        <v>-0.3047943396156181</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.689681972592316</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.939154369841003</v>
+        <v>-8.841214077298337</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4588560174275553</v>
+        <v>-0.4196799004104892</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.758425108326195</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.062398759056432</v>
+        <v>-8.964458466513767</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5121800776481304</v>
+        <v>-0.4730039606310643</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.758425108326195</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.445400147799063</v>
+        <v>-9.347459855256398</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6654827344667669</v>
+        <v>-0.6263066174497007</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.758425108326195</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.602799028012184</v>
+        <v>-9.504858735469519</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.7258707705805851</v>
+        <v>-0.686694653563519</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.915823988539316</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.962329350516185</v>
+        <v>-9.86438905797352</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8643325962841355</v>
+        <v>-0.8251564792670694</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.915823988539316</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.01267841397041</v>
+        <v>-9.914738121427742</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8765562017086466</v>
+        <v>-0.8373800846915809</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.966173051993538</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.2318273820446</v>
+        <v>-10.13388708950194</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9611740383165572</v>
+        <v>-0.9219979212994907</v>
       </c>
       <c r="F1876" t="n">
         <v>-2.185322020067736</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.22813645708819</v>
+        <v>-10.13019616454553</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9596976683339924</v>
+        <v>-0.9205215513169267</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.185322020067736</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.43239463241806</v>
+        <v>-10.33445433987539</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.035887741347295</v>
+        <v>-0.9967116243302296</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.312960964681725</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.65043240404924</v>
+        <v>-10.55249211150657</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.118620295515331</v>
+        <v>-1.079444178498264</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.487731732777624</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.57696257238179</v>
+        <v>-10.47902227983912</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.07386066135493</v>
+        <v>-1.034684544337864</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.414261901110175</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.75208698976833</v>
+        <v>-10.65414669722566</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.12935520756203</v>
+        <v>-1.090179090544964</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.589386318496719</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.98653908378282</v>
+        <v>-10.88859879124015</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.230355210069422</v>
+        <v>-1.191179093052356</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.589386318496719</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.27434292832006</v>
+        <v>-11.17640263577739</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.352148938658294</v>
+        <v>-1.312972821641228</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.877190163033957</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.32712908392038</v>
+        <v>-11.22918879137772</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.372147611059868</v>
+        <v>-1.332971494042802</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.972865649616354</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.4920980657674</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.55915800365665</v>
+        <v>-11.46121771111398</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.462265450325259</v>
+        <v>-1.423089333308192</v>
       </c>
       <c r="F1885" t="n">
         <v>-3.034878346804777</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.50714248968783</v>
+        <v>-11.40920219714517</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.437468909051332</v>
+        <v>-1.398292792034266</v>
       </c>
       <c r="F1886" t="n">
         <v>-3.034878346804777</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.64881433141195</v>
+        <v>-11.55087403886929</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.495612872639722</v>
+        <v>-1.456436755622656</v>
       </c>
       <c r="F1887" t="n">
         <v>-3.034878346804777</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.59922348698712</v>
+        <v>-11.50128319444445</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.460723124704916</v>
+        <v>-1.42154700768785</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.985287502379943</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.40007137975002</v>
+        <v>-11.30213108720736</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.394113415456759</v>
+        <v>-1.354937298439693</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.81996497643013</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.17422622703061</v>
+        <v>-11.07628593448795</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.294196281332786</v>
+        <v>-1.255020164315721</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.778038300842967</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.04964757069302</v>
+        <v>-10.95170727815035</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.24322567424169</v>
+        <v>-1.204049557224625</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.778038300842967</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.1025428587373</v>
+        <v>-11.00460256619464</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.261750015297298</v>
+        <v>-1.222573898280232</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.77308295475452</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.81863412780855</v>
+        <v>-10.72069383526589</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.142452818687161</v>
+        <v>-1.103276701670096</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.77308295475452</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.74726773519891</v>
+        <v>-10.64932744265624</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.123643524037168</v>
+        <v>-1.084467407020102</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.701716562144873</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.48343086799484</v>
+        <v>-10.38549057545217</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.027992258468447</v>
+        <v>-0.9888161414513816</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.701716562144873</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.21618906712644</v>
+        <v>-10.11824877458378</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.9229300986204616</v>
+        <v>-0.8837539816033968</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.701716562144873</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.11828202844995</v>
+        <v>-10.02034173590729</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8840675981233264</v>
+        <v>-0.8448914811062616</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.633730812284316</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.09432848747399</v>
+        <v>-9.996388194931328</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8738176755874494</v>
+        <v>-0.8346415585703846</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.609777271308359</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.830268549151194</v>
+        <v>-9.732328256608531</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7814540164200832</v>
+        <v>-0.7422778994030179</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.345717332985563</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.123188925646357</v>
+        <v>-9.025248633103693</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.5014092006784492</v>
+        <v>-0.4622330836613839</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.345717332985563</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.083004627280166</v>
+        <v>-8.985064334737503</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4849918574441316</v>
+        <v>-0.4458157404270664</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.305533034619372</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.002934831742362</v>
+        <v>-8.904994539199699</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4535971180082528</v>
+        <v>-0.4144210009911875</v>
       </c>
       <c r="F1902" t="n">
         <v>-2.225463239081568</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.769453609512762</v>
+        <v>-8.671513316970099</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3522802002785608</v>
+        <v>-0.3131040832614955</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.991982016851969</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.619787218505248</v>
+        <v>-8.521846925962585</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2953058541885141</v>
+        <v>-0.2561297371714488</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.899078525609433</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.487511744874361</v>
+        <v>-8.389571452331698</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2470281779891321</v>
+        <v>-0.2078520609720669</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.766803051978547</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.296912070201207</v>
+        <v>-8.198971777658544</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1679732474322342</v>
+        <v>-0.1287971304151689</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.576203377305394</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.047912271517626</v>
+        <v>-7.949971978974963</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.05546698673514294</v>
+        <v>-0.01629086971807769</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.576203377305394</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.153502261290731</v>
+        <v>-8.055561968748068</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2256789122436036</v>
+        <v>-0.1865027952265379</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.681793367078498</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.172237163409328</v>
+        <v>-8.074296870866664</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1846285312139559</v>
+        <v>-0.1454524141968907</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.681793367078498</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.024297122001729</v>
+        <v>-7.926356829459065</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2453314373390838</v>
+        <v>-0.2061553203220186</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.661472451169941</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.000068485612756</v>
+        <v>-7.902128193070093</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2443539690369727</v>
+        <v>-0.2051778520199075</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.637243814780968</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.956520078842066</v>
+        <v>-7.858579786299402</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2338952184237897</v>
+        <v>-0.1947191014067244</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.637243814780968</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.714371685388207</v>
+        <v>-7.616431392845544</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1225735066611033</v>
+        <v>-0.08339738964403809</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.637243814780968</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.651142313619859</v>
+        <v>-7.553202021077196</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1027496374945693</v>
+        <v>-0.06357352047750364</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.637243814780968</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.527851178802728</v>
+        <v>-7.429910886260065</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.05593508955713977</v>
+        <v>-0.01675897254007452</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.513952679963838</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.506701979899285</v>
+        <v>-7.408761687356622</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.03977443175843742</v>
+        <v>-0.0005983147413721746</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.492803481060395</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788095</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.262936537915841</v>
+        <v>-7.164996245373177</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.05351245338199107</v>
+        <v>0.09268857039905631</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.492803481060395</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.998908470722581</v>
+        <v>-6.900968178179918</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1612479941793108</v>
+        <v>0.200424111196376</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.290938082244441</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.749058076773506</v>
+        <v>-6.651117784230843</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2539302267426429</v>
+        <v>0.2931063437597081</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.290938082244441</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.573165984306074</v>
+        <v>-6.475225691763411</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3278861872502645</v>
+        <v>0.3670623042673298</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.290938082244441</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.401719521283611</v>
+        <v>-6.303779228740948</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4097922785138035</v>
+        <v>0.4489683955308688</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.119491619221978</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.176686521614788</v>
+        <v>-6.078746229072125</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4988259559976296</v>
+        <v>0.5380020730146948</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.8944586195531549</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.962052143978381</v>
+        <v>-5.864111851435718</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5893745081065096</v>
+        <v>0.6285506251235748</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.6798242419167481</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.869052102772483</v>
+        <v>-5.77111181022982</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6077687833726646</v>
+        <v>0.6469449003897298</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.6798242419167481</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.628621605967623</v>
+        <v>-5.530681313424959</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7056840587194859</v>
+        <v>0.7448601757365516</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.4393937451118878</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.556379037796428</v>
+        <v>-5.458438745253765</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.738510399822784</v>
+        <v>0.7776865168398497</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.4393937451118878</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.440439188171243</v>
+        <v>-5.342498895628579</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7855649235901985</v>
+        <v>0.8247410406072637</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.3625720140957639</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.19778359974808</v>
+        <v>-5.099843307205417</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8796252301794567</v>
+        <v>0.9188013471965224</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.3625720140957639</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.977762801711069</v>
+        <v>-4.879822509168406</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9692125864048753</v>
+        <v>1.008388703421941</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.2213521690277837</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.844895112647792</v>
+        <v>-4.746954820105128</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.03825384483201</v>
+        <v>1.077429961849075</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.2213521690277837</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.685380009128422</v>
+        <v>-4.587439716585759</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.103205730680059</v>
+        <v>1.142381847697125</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.06183706550841372</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.540707864028684</v>
+        <v>-4.442767571486021</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.171162691281394</v>
+        <v>1.21033880829846</v>
       </c>
       <c r="F1932" t="n">
         <v>0.08283507959132369</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.600582691386377</v>
+        <v>-4.502642398843713</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.133250251739743</v>
+        <v>1.172426368756808</v>
       </c>
       <c r="F1933" t="n">
         <v>0.02296025223363157</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.513783193607368</v>
+        <v>-4.415842901064705</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.190370544173913</v>
+        <v>1.229546661190978</v>
       </c>
       <c r="F1934" t="n">
         <v>0.02296025223363157</v>
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900692</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.996312647304019</v>
+        <v>2.989728453122251</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.516252900069174</v>
+        <v>-4.418312607526511</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.189455062962602</v>
+        <v>1.222046985797899</v>
       </c>
       <c r="F1935" t="n">
         <v>0.02049054577182541</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.008606974767115</v>
+        <v>3.002022780585347</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473598</v>
+        <v>3.743216620473599</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.007319569778721</v>
+        <v>3.000735375596953</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.584623086393185</v>
+        <v>-4.486682793850521</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.1731139109077</v>
+        <v>1.205705833742997</v>
       </c>
       <c r="F1936" t="n">
         <v>0.02976624480804035</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.025179316663546</v>
+        <v>3.018595122481778</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978367</v>
+        <v>3.714175563978368</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.997756278410613</v>
+        <v>2.991172084228845</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.463206656766708</v>
+        <v>-4.365266364224045</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.212117191390182</v>
+        <v>1.244709114225479</v>
       </c>
       <c r="F1937" t="n">
         <v>0.02976624480804035</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.015616025295437</v>
+        <v>3.009031831113669</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887701</v>
+        <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.822465843450999</v>
+        <v>2.815881649269231</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.494199816095414</v>
+        <v>-4.39625952355275</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.024429492699087</v>
+        <v>1.057021415534384</v>
       </c>
       <c r="F1938" t="n">
         <v>0.02976624480804035</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.840325590335824</v>
+        <v>2.833741396154056</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675899</v>
+        <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.827033075442787</v>
+        <v>2.820448881261019</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.318725556302944</v>
+        <v>-4.220785263760281</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.099186428607863</v>
+        <v>1.13177835144316</v>
       </c>
       <c r="F1939" t="n">
         <v>0.02976624480804035</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.844892822327612</v>
+        <v>2.838308628145843</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695444</v>
+        <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.802775104203994</v>
+        <v>2.796190910022226</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.429661808944193</v>
+        <v>-4.331721516401529</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.03055395631257</v>
+        <v>1.063145879147867</v>
       </c>
       <c r="F1940" t="n">
         <v>0.02976624480804035</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.820634851088819</v>
+        <v>2.81405065690705</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581289</v>
+        <v>3.77320672158129</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.8059064894239</v>
+        <v>2.799322295242132</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.632688386487426</v>
+        <v>-4.534748093944763</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9524747105151823</v>
+        <v>0.9850666333504794</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.173260332735193</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.701950289782785</v>
+        <v>2.695366095601016</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.816078875856032</v>
+        <v>2.809494681674264</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.474762787552133</v>
+        <v>-4.37682249500947</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.025817336521432</v>
+        <v>1.058409259356729</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.173260332735193</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.712122676214917</v>
+        <v>2.705538482033149</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.811025146429893</v>
+        <v>2.804440952248124</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.388519324525755</v>
+        <v>-4.290579031983092</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.055260992305843</v>
+        <v>1.08785291514114</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.173260332735193</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.707068946788777</v>
+        <v>2.700484752607009</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.802800921874418</v>
+        <v>2.79621672769265</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.389702409176817</v>
+        <v>-4.291762116634153</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.046563533889944</v>
+        <v>1.079155456725241</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.1789033812017046</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.695458893153396</v>
+        <v>2.688874698971627</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.80335279490752</v>
+        <v>2.796768600725752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.266574702182734</v>
+        <v>-4.16863440964007</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.096366489720679</v>
+        <v>1.128958412555976</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.1789033812017046</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.696010766186497</v>
+        <v>2.689426572004729</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.732625486798885</v>
+        <v>2.726041292617117</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.173764220731874</v>
+        <v>-4.075823928189211</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.062763374192389</v>
+        <v>1.095355297027686</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.08609289975084522</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.680969746948378</v>
+        <v>2.67438555276661</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.734498962723486</v>
+        <v>2.727914768541718</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.125201168510844</v>
+        <v>-4.027260875968181</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.084062071005401</v>
+        <v>1.116653993840699</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.03752984752981503</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.711981054205598</v>
+        <v>2.705396860023829</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.729574671235209</v>
+        <v>2.722990477053441</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.012529950274594</v>
+        <v>-3.914589657731931</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.124206266811624</v>
+        <v>1.156798189646921</v>
       </c>
       <c r="F1948" t="n">
         <v>0.07514137070643517</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.774659493659071</v>
+        <v>2.768075299477303</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.735065967065876</v>
+        <v>2.728481772884108</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.900152949091921</v>
+        <v>-3.8887116732396</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.174648363115361</v>
+        <v>1.172640679274521</v>
       </c>
       <c r="F1949" t="n">
         <v>0.07514137070643517</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.780150789489738</v>
+        <v>2.77356659530797</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.746563168834415</v>
+        <v>2.739978974652647</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.098387517978652</v>
+        <v>-4.086946242126331</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.106851737329207</v>
+        <v>1.104844053488368</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1230931981802954</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.672707249926238</v>
+        <v>2.66612305574447</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.584918888835069</v>
+        <v>2.578334694653301</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.181388799003931</v>
+        <v>-4.16994752315161</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9120069449197492</v>
+        <v>0.9099992610789094</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1416640827074692</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.499920439210587</v>
+        <v>2.493336245028819</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.705068549554274</v>
+        <v>2.698484355372506</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.022194526947354</v>
+        <v>-4.010753251095034</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.095834314461585</v>
+        <v>1.093826630620745</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1416640827074692</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.620070099929793</v>
+        <v>2.613485905748025</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.719581575656597</v>
+        <v>2.712997381474829</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.108793109928457</v>
+        <v>-4.097351834076137</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.075707907371467</v>
+        <v>1.073700223530627</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1416640827074692</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.634583126032116</v>
+        <v>2.627998931850348</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.717001016998966</v>
+        <v>2.710416822817198</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.070409447370306</v>
+        <v>-4.058968171517986</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.088480813737096</v>
+        <v>1.086473129896256</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.103280420149318</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.655032764909376</v>
+        <v>2.648448570727608</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.713730045844268</v>
+        <v>2.7071458516625</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.89329311733514</v>
+        <v>-3.88185184148282</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.156056374596465</v>
+        <v>1.154048690755625</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.103280420149318</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.651761793754678</v>
+        <v>2.64517759957291</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.714413437606181</v>
+        <v>2.707829243424413</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.863590993358846</v>
+        <v>-3.852149717506526</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.168620615948895</v>
+        <v>1.166612932108056</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.1077505453646314</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.649763110387402</v>
+        <v>2.643178916205635</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750725801481235</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.708200412912595</v>
+        <v>2.701616218730828</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.684215572120078</v>
+        <v>-3.672774296267758</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.234157759750817</v>
+        <v>1.232150075909977</v>
       </c>
       <c r="F1957" t="n">
         <v>0.04902621280608732</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.737616140596248</v>
+        <v>2.73103194641448</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.689007868244185</v>
+        <v>2.682423674062417</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.729229785640685</v>
+        <v>-3.717788509788365</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.196959529674164</v>
+        <v>1.194951845833324</v>
       </c>
       <c r="F1958" t="n">
         <v>0.01867731749148271</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.700214258739075</v>
+        <v>2.693630064557307</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.694699430583131</v>
+        <v>2.688115236401363</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.99623429591312</v>
+        <v>-3.9847930200608</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.095849287904135</v>
+        <v>1.093841604063296</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1756857205514659</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.589287998252252</v>
+        <v>2.582703804070484</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.693903352479632</v>
+        <v>2.687319158297865</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.285021516372035</v>
+        <v>-4.273580240519715</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.979538321617071</v>
+        <v>0.9775306377762312</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2767718406504662</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.527840248089353</v>
+        <v>2.521256053907585</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.691503314033949</v>
+        <v>2.684919119852181</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.252545930201263</v>
+        <v>-4.241104654348943</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9901285176396966</v>
+        <v>0.988120833798857</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2767718406504662</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.52544020964367</v>
+        <v>2.518856015461902</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.688028033242194</v>
+        <v>2.681443839060426</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.233507802493966</v>
+        <v>-4.222066526641646</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9942684879308603</v>
+        <v>0.9922608040900207</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3349554519816608</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.487054762053198</v>
+        <v>2.48047056787143</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601248</v>
+        <v>3.73106089760125</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.865609902180875</v>
+        <v>2.859025707999107</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.250253667750341</v>
+        <v>-4.238812391898021</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.165152010766991</v>
+        <v>1.163144326926151</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3349554519816608</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.664636630991879</v>
+        <v>2.658052436810111</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.558875345260864</v>
+        <v>3.415604731774791</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.866538266697957</v>
+        <v>2.85985903698524</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.250253667750341</v>
+        <v>-4.1547731855133</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.165152010766991</v>
+        <v>1.197593338466173</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3349554519816608</v>
+        <v>-0.4037967567645305</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.859602063684325</v>
+        <v>2.617580982926522</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240514.xlsx
+++ b/tame_output/ON/bt/strategyON_20240514.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.5%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.8%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-25.6%</t>
+          <t>-35.3%</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>112.9%</t>
+          <t>112.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>132.6%</t>
+          <t>131.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,17 +977,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-697.2%</t>
+          <t>-675.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.4%</t>
+          <t>-52.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.5%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.8%</t>
+          <t>453.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-577.1%</t>
+          <t>-584.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,27 +1135,27 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-279.3%</t>
+          <t>-270.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-42.3%</t>
+          <t>-39.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-28.3%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>762.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-256.5%</t>
+          <t>-269.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.3%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-312.6%</t>
+          <t>-290.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-247.0%</t>
+          <t>-152.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-264.4%</t>
+          <t>-255.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-188.0%</t>
+          <t>-174.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-184.3%</t>
+          <t>-188.5%</t>
         </is>
       </c>
     </row>
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.270535311690021</v>
+        <v>-1.050362663282183</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.608509900961274</v>
+        <v>2.696578960324409</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9518971397600179</v>
+        <v>1.172069788167855</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.68821873380704</v>
+        <v>3.820322322851743</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.27116857953743</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.492157245248138</v>
+        <v>-1.271984596840301</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.519727344136949</v>
+        <v>2.607796403500084</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.9143710060726489</v>
+        <v>1.134543654480486</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.665569270193541</v>
+        <v>3.797672859238243</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.700161303601216</v>
+        <v>-1.479988655193378</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.441417865349643</v>
+        <v>2.529486924712778</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.9143710060726489</v>
+        <v>1.134543654480486</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.670461414747466</v>
+        <v>3.802565003792168</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.911573724489191</v>
+        <v>-1.691401076081353</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.351934353332441</v>
+        <v>2.440003412695576</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.7029585851846738</v>
+        <v>0.9231312335925113</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.538695418552669</v>
+        <v>3.670799007597371</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.250732102077713</v>
+        <v>-2.030559453669875</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.209355301603481</v>
+        <v>2.297424360966616</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.3638002075961517</v>
+        <v>0.5839728560039892</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.328284691306005</v>
+        <v>3.460388280350708</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.459222883529397</v>
+        <v>-2.23905023512156</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.146297278761576</v>
+        <v>2.234366338124711</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1553094261444673</v>
+        <v>0.3754820745523048</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.223528512173762</v>
+        <v>3.355632101218465</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.952547755064575</v>
+        <v>-2.732375106656738</v>
       </c>
       <c r="E1853" t="n">
-        <v>1.957066080556073</v>
+        <v>2.045135139919208</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.05032331190484857</v>
+        <v>0.270495960312686</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.16863559403856</v>
+        <v>3.300739183083262</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382331</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.444932783088672</v>
+        <v>-3.224760134680835</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.761218461390166</v>
+        <v>1.849287520753301</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4420617161192482</v>
+        <v>-0.2218890677114107</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.874310969267834</v>
+        <v>3.006414558312537</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.830113174018745</v>
+        <v>-3.609940525610907</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.605688843831001</v>
+        <v>1.693757903194136</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4420617161192482</v>
+        <v>-0.2218890677114107</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.872853508080697</v>
+        <v>3.0049570971254</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-4.173795947245408</v>
+        <v>-3.95362329883757</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.469984857994952</v>
+        <v>1.558053917358087</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.5499677681464663</v>
+        <v>-0.3297951197386289</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.809879000318983</v>
+        <v>2.941982589363685</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.380307724132429</v>
+        <v>-4.160135075724591</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.383486205896401</v>
+        <v>1.471555265259536</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.7564795450334878</v>
+        <v>-0.5363068966256503</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.682077992843027</v>
+        <v>2.81418158188773</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.68954182712848</v>
+        <v>-4.469369178720642</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.26156549139824</v>
+        <v>1.349634550761375</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.7564795450334878</v>
+        <v>-0.5363068966256503</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.683850919543287</v>
+        <v>2.81595450858799</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-5.121347620278267</v>
+        <v>-4.90117497187043</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.07517606160573</v>
+        <v>1.163245120968865</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8928970414747548</v>
+        <v>-0.6727243930669173</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.588333309145932</v>
+        <v>2.720436898190634</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.356041614410819</v>
+        <v>-5.135868966002982</v>
       </c>
       <c r="E1860" t="n">
-        <v>0.9695832389547996</v>
+        <v>1.057652298317934</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.8865607742454996</v>
+        <v>-0.6663881258376622</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.580419844485575</v>
+        <v>2.712523433530277</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.691704261641272</v>
+        <v>-5.471531613233434</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8338987717185837</v>
+        <v>0.9219678310817185</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.8865607742454996</v>
+        <v>-0.6663881258376622</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.57900043614154</v>
+        <v>2.711104025186243</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-6.055330506541585</v>
+        <v>-5.835157858133748</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.6949358339926999</v>
+        <v>0.7830048933558347</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.9847824111126254</v>
+        <v>-0.764609762704788</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.526555014255506</v>
+        <v>2.658658603300209</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.420457889180332</v>
+        <v>-6.200285240772494</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5481393959430325</v>
+        <v>0.6362084553061673</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.281093195411638</v>
+        <v>-1.060920547003801</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.34802305868193</v>
+        <v>2.480126647726633</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.829046666361011</v>
+        <v>-6.608874017953173</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.3834654290855202</v>
+        <v>0.471534488448655</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.469509324184479</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.101631336388282</v>
+        <v>2.233734925432985</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.242029150502105</v>
+        <v>-7.021856502094267</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.213457867900543</v>
+        <v>0.3015269272636782</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.469509324184479</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.096816768859743</v>
+        <v>2.228920357904445</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.658421024789102</v>
+        <v>-7.438248376381265</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.0448951687946213</v>
+        <v>0.1329642281577565</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.469509324184479</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.09481081946862</v>
+        <v>2.226914408513323</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-8.035098035318946</v>
+        <v>-7.814925386911109</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.09551694474863703</v>
+        <v>-0.007447885385502229</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.469509324184479</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.105069510137299</v>
+        <v>2.237173099182002</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.380972857303755</v>
+        <v>-8.160800208895918</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.2377673083968657</v>
+        <v>-0.1496982490337304</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.469509324184479</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.101169075282995</v>
+        <v>2.233272664327697</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.544552735488139</v>
+        <v>-8.324380087080302</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3047943396156181</v>
+        <v>-0.2167252802524833</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.689681972592316</v>
+        <v>-1.469509324184479</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.099573995337995</v>
+        <v>2.231677584382698</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.841214077298337</v>
+        <v>-8.6210414288905</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4196799004104892</v>
+        <v>-0.3316108410473544</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.758425108326195</v>
+        <v>-1.538252459918358</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.062107089826876</v>
+        <v>2.194210678871579</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.964458466513767</v>
+        <v>-8.744285818105929</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.4730039606310643</v>
+        <v>-0.3849349012679291</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.758425108326195</v>
+        <v>-1.538252459918358</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.058080785292473</v>
+        <v>2.190184374337176</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.347459855256398</v>
+        <v>-9.12728720684856</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6263066174497007</v>
+        <v>-0.5382375580865659</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.758425108326195</v>
+        <v>-1.538252459918358</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.057978683970889</v>
+        <v>2.190082273015592</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.504858735469519</v>
+        <v>-9.284686087061681</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.686694653563519</v>
+        <v>-0.5986255942003837</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.915823988539316</v>
+        <v>-1.695651340131479</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.966110871814446</v>
+        <v>2.098214460859149</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.86438905797352</v>
+        <v>-9.644216409565683</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8251564792670694</v>
+        <v>-0.7370874199039346</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.915823988539316</v>
+        <v>-1.695651340131479</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.971461175112497</v>
+        <v>2.103564764157199</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.914738121427742</v>
+        <v>-9.694565473019905</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.8373800846915809</v>
+        <v>-0.7493110253284456</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.966173051993538</v>
+        <v>-1.746000403585701</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.949167756997141</v>
+        <v>2.081271346041843</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.13388708950194</v>
+        <v>-9.913714441094102</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.9219979212994907</v>
+        <v>-0.8339288619363558</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.185322020067736</v>
+        <v>-1.965149371659898</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.820720126774391</v>
+        <v>1.952823715819094</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.13019616454553</v>
+        <v>-9.910023516137692</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.9205215513169267</v>
+        <v>-0.8324524919537915</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.185322020067736</v>
+        <v>-1.965149371659898</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.820720126774391</v>
+        <v>1.952823715819094</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.33445433987539</v>
+        <v>-10.11428169146756</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.9967116243302296</v>
+        <v>-0.9086425649670948</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.312960964681725</v>
+        <v>-2.092788316273887</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.74964995712464</v>
+        <v>1.881753546169343</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.55249211150657</v>
+        <v>-10.33231946309873</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.079444178498264</v>
+        <v>-0.9913751191351294</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.487731732777624</v>
+        <v>-2.267559084369786</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.649270050751537</v>
+        <v>1.781373639796239</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.47902227983912</v>
+        <v>-10.25884963143128</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.034684544337864</v>
+        <v>-0.9466154849747292</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.414261901110175</v>
+        <v>-2.194089252702338</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.708723651245427</v>
+        <v>1.84082724029013</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900556660786</v>
+        <v>3.490055666078599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.65414669722566</v>
+        <v>-10.43397404881783</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.090179090544964</v>
+        <v>-1.00211003118183</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.589386318496719</v>
+        <v>-2.369213670088882</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.618204221561018</v>
+        <v>1.75030781060572</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880273</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.88859879124015</v>
+        <v>-10.66842614283232</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.191179093052356</v>
+        <v>-1.103110033689222</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.589386318496719</v>
+        <v>-2.369213670088882</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.610985056659422</v>
+        <v>1.743088645704124</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.17640263577739</v>
+        <v>-10.95622998736956</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.312972821641228</v>
+        <v>-1.224903762278093</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.877190163033957</v>
+        <v>-2.65701751462612</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.431630559163103</v>
+        <v>1.563734148207805</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.22918879137772</v>
+        <v>-11.00901614296988</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.332971494042802</v>
+        <v>-1.244902434679667</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.972865649616354</v>
+        <v>-2.752693001208517</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.375341057052221</v>
+        <v>1.507444646096923</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.46121771111398</v>
+        <v>-11.24104506270614</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.423089333308192</v>
+        <v>-1.335020273945057</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.034878346804777</v>
+        <v>-2.81470569839694</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.340827167368281</v>
+        <v>1.472930756412984</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.40920219714517</v>
+        <v>-11.18902954873733</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.398292792034266</v>
+        <v>-1.310223732671131</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.034878346804777</v>
+        <v>-2.81470569839694</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.344817503054682</v>
+        <v>1.476921092099385</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628922</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.55087403886929</v>
+        <v>-11.33070139046145</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.456436755622656</v>
+        <v>-1.368367696259521</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.034878346804777</v>
+        <v>-2.81470569839694</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.343342276155941</v>
+        <v>1.475445865200643</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.50128319444445</v>
+        <v>-11.28111054603662</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.42154700768785</v>
+        <v>-1.333477948324715</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.985287502379943</v>
+        <v>-2.765114853972106</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.388150192975713</v>
+        <v>1.520253782020416</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.30213108720736</v>
+        <v>-11.08195843879952</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.354937298439693</v>
+        <v>-1.266868239076559</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.81996497643013</v>
+        <v>-2.599792328022293</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.474292574898918</v>
+        <v>1.606396163943621</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.07628593448795</v>
+        <v>-10.85611328608011</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.255020164315721</v>
+        <v>-1.166951104952585</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.778038300842967</v>
+        <v>-2.557865652435129</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.509027653287425</v>
+        <v>1.641131242332128</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.95170727815035</v>
+        <v>-10.73153462974251</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.204049557224625</v>
+        <v>-1.11598049786149</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.778038300842967</v>
+        <v>-2.557865652435129</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.510166797843484</v>
+        <v>1.642270386888186</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.00460256619464</v>
+        <v>-10.7844299177868</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.222573898280232</v>
+        <v>-1.134504838917096</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.77308295475452</v>
+        <v>-2.552910306346683</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.515773779658659</v>
+        <v>1.647877368703362</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.72069383526589</v>
+        <v>-10.50052118685805</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.103276701670096</v>
+        <v>-1.015207642306961</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.77308295475452</v>
+        <v>-2.552910306346683</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.521507483897296</v>
+        <v>1.653611072941998</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.64932744265624</v>
+        <v>-10.4291547942484</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.084467407020102</v>
+        <v>-0.9963983476569664</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.701716562144873</v>
+        <v>-2.481543913737035</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.554590057069219</v>
+        <v>1.686693646113922</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.38549057545217</v>
+        <v>-10.16531792704433</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9888161414513816</v>
+        <v>-0.9007470820882459</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.701716562144873</v>
+        <v>-2.481543913737035</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.544706575756312</v>
+        <v>1.676810164801014</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.11824877458378</v>
+        <v>-9.898076126175937</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8837539816033968</v>
+        <v>-0.7956849222402611</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.701716562144873</v>
+        <v>-2.481543913737035</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.542872015256938</v>
+        <v>1.67497560430164</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.02034173590729</v>
+        <v>-9.800169087499446</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8448914811062616</v>
+        <v>-0.7568224217431254</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.633730812284316</v>
+        <v>-2.413558163876479</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.583363150199811</v>
+        <v>1.715466739244514</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.996388194931328</v>
+        <v>-9.776215546523488</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8346415585703846</v>
+        <v>-0.7465724992072489</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.609777271308359</v>
+        <v>-2.389604622900521</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.598403780930879</v>
+        <v>1.730507369975582</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.732328256608531</v>
+        <v>-9.512155608200692</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7422778994030179</v>
+        <v>-0.6542088400398822</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.345717332985563</v>
+        <v>-2.125544684577725</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.743579427762805</v>
+        <v>1.875683016807507</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.025248633103693</v>
+        <v>-8.805075984695854</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4622330836613839</v>
+        <v>-0.3741640242982482</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.345717332985563</v>
+        <v>-2.125544684577725</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.740792394102504</v>
+        <v>1.872895983147206</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.985064334737503</v>
+        <v>-8.764891686329664</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4458157404270664</v>
+        <v>-0.3577466810639307</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.305533034619372</v>
+        <v>-2.085360386211534</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.765246597010059</v>
+        <v>1.897350186054762</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.904994539199699</v>
+        <v>-8.684821890791859</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.4144210009911875</v>
+        <v>-0.3263519416280518</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.225463239081568</v>
+        <v>-2.00529059067373</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.812655295553499</v>
+        <v>1.944758884598201</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.671513316970099</v>
+        <v>-8.45134066856226</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.3131040832614955</v>
+        <v>-0.2250350238983598</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.991982016851969</v>
+        <v>-1.771809368444132</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.960668457729111</v>
+        <v>2.092772046773813</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.521846925962585</v>
+        <v>-8.301674277554746</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2561297371714488</v>
+        <v>-0.1680606778083131</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.899078525609433</v>
+        <v>-1.678905877201596</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.013518342161673</v>
+        <v>2.145621931206375</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.389571452331698</v>
+        <v>-8.169398803923858</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.2078520609720669</v>
+        <v>-0.1197830016089312</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.766803051978547</v>
+        <v>-1.546630403570709</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.088251113087232</v>
+        <v>2.220354702131934</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.198971777658544</v>
+        <v>-7.978799129250706</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.1287971304151689</v>
+        <v>-0.04072807105203324</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.576203377305394</v>
+        <v>-1.356030728897556</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.20542597857876</v>
+        <v>2.337529567623463</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.949971978974963</v>
+        <v>-7.729799330567125</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.01629086971807769</v>
+        <v>0.07177818964505756</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.576203377305394</v>
+        <v>-1.356030728897556</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.218332319802419</v>
+        <v>2.350435908847121</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.055561968748068</v>
+        <v>-7.835389320340229</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1865027952265379</v>
+        <v>-0.09843373586340265</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.681793367078498</v>
+        <v>-1.461620718670661</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.027002396339338</v>
+        <v>2.15910598538404</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457902</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.074296870866664</v>
+        <v>-7.854124222458826</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1454524141968907</v>
+        <v>-0.05738335483375501</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.681793367078498</v>
+        <v>-1.461620718670661</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.075546738216424</v>
+        <v>2.207650327261127</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.926356829459065</v>
+        <v>-7.706184181051227</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2061553203220186</v>
+        <v>-0.1180862609588829</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.661472451169941</v>
+        <v>-1.441299802762103</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.967860365073391</v>
+        <v>2.099963954118094</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.902128193070093</v>
+        <v>-7.681955544662254</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2051778520199075</v>
+        <v>-0.1171087926567722</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.637243814780968</v>
+        <v>-1.417071166373131</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.973683560653296</v>
+        <v>2.105787149697999</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.858579786299402</v>
+        <v>-7.638407137891564</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1947191014067244</v>
+        <v>-0.1066500420435892</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.637243814780968</v>
+        <v>-1.417071166373131</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.966722948558203</v>
+        <v>2.098826537602906</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.616431392845544</v>
+        <v>-7.396258744437706</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.08339738964403809</v>
+        <v>0.00467166971909716</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.637243814780968</v>
+        <v>-1.417071166373131</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.981185302939346</v>
+        <v>2.113288891984049</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.553202021077196</v>
+        <v>-7.333029372669357</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.06357352047750364</v>
+        <v>0.02449553888563161</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.637243814780968</v>
+        <v>-1.417071166373131</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.975717423398541</v>
+        <v>2.107821012443244</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.429910886260065</v>
+        <v>-7.209738237852227</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.01675897254007452</v>
+        <v>0.07131008682306073</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.513952679963838</v>
+        <v>-1.293780031556</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.047190198299396</v>
+        <v>2.179293787344099</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.408761687356622</v>
+        <v>-7.188589038948783</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.0005983147413721746</v>
+        <v>0.08747074462176307</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.492803481060395</v>
+        <v>-1.272630832652557</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.067580695878787</v>
+        <v>2.19968428492349</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.164996245373177</v>
+        <v>-6.944823596965339</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.09268857039905631</v>
+        <v>0.1807576297621916</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.492803481060395</v>
+        <v>-1.272630832652557</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.063361404225838</v>
+        <v>2.195464993270541</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.900968178179918</v>
+        <v>-6.680795529772078</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.200424111196376</v>
+        <v>0.2884931705595117</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.290938082244441</v>
+        <v>-1.070765433836603</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.186604957435426</v>
+        <v>2.318708546480129</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.651117784230843</v>
+        <v>-6.430945135823004</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2931063437597081</v>
+        <v>0.3811754031228438</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.290938082244441</v>
+        <v>-1.070765433836603</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.179347032419129</v>
+        <v>2.311450621463831</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.475225691763411</v>
+        <v>-6.255053043355572</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3670623042673298</v>
+        <v>0.4551313636304655</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.290938082244441</v>
+        <v>-1.070765433836603</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.182946155939777</v>
+        <v>2.31504974498448</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.303779228740948</v>
+        <v>-6.083606580333108</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4489683955308688</v>
+        <v>0.5370374548940045</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.119491619221978</v>
+        <v>-0.8993189708141404</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.299141539807809</v>
+        <v>2.431245128852511</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.078746229072125</v>
+        <v>-5.858573580664285</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5380020730146948</v>
+        <v>0.6260711323778305</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8944586195531549</v>
+        <v>-0.6742859711453175</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.4331818172254</v>
+        <v>2.565285406270102</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.864111851435718</v>
+        <v>-5.643939203027879</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6285506251235748</v>
+        <v>0.7166196844867105</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6798242419167481</v>
+        <v>-0.4596515935089107</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.566657244861561</v>
+        <v>2.698760833906263</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.77111181022982</v>
+        <v>-5.55093916182198</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6469449003897298</v>
+        <v>0.7350139597528655</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6798242419167481</v>
+        <v>-0.4596515935089107</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.547851503645357</v>
+        <v>2.679955092690059</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.530681313424959</v>
+        <v>-5.31050866501712</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7448601757365516</v>
+        <v>0.8329292350996873</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4393937451118878</v>
+        <v>-0.2192210967040504</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.69385287835315</v>
+        <v>2.825956467397853</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.458438745253765</v>
+        <v>-5.238266096845925</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7776865168398497</v>
+        <v>0.8657555762029854</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4393937451118878</v>
+        <v>-0.2192210967040504</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.69778219218797</v>
+        <v>2.829885781232673</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.342498895628579</v>
+        <v>-5.12232624722074</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8247410406072637</v>
+        <v>0.9128100999703994</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3625720140957639</v>
+        <v>-0.1423993656879265</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.744553814714985</v>
+        <v>2.876657403759687</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.099843307205417</v>
+        <v>-4.879670658797577</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9188013471965224</v>
+        <v>1.006870406559658</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3625720140957639</v>
+        <v>-0.1423993656879265</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.741551885934978</v>
+        <v>2.87365547497968</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.879822509168406</v>
+        <v>-4.659649860760567</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.008388703421941</v>
+        <v>1.096457762785076</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2213521690277837</v>
+        <v>-0.001179520619946306</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.82786282998638</v>
+        <v>2.959966419031083</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.746954820105128</v>
+        <v>-4.526782171697289</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.077429961849075</v>
+        <v>1.165499021212211</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2213521690277837</v>
+        <v>-0.001179520619946306</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.843757012788203</v>
+        <v>2.975860601832906</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.587439716585759</v>
+        <v>-4.367267068177919</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.142381847697125</v>
+        <v>1.230450907060261</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.06183706550841372</v>
+        <v>0.1583355828994236</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.940611919340127</v>
+        <v>3.07271550838483</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.442767571486021</v>
+        <v>-4.222594923078182</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.21033880829846</v>
+        <v>1.298407867661595</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.08283507959132369</v>
+        <v>0.303007727999161</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.03750330896141</v>
+        <v>3.169606898006112</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.502642398843713</v>
+        <v>-4.282469750435874</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.172426368756808</v>
+        <v>1.260495428119944</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.02296025223363157</v>
+        <v>0.2431329006414689</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.98761590394822</v>
+        <v>3.119719492992923</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.415842901064705</v>
+        <v>-4.195670252656866</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.229546661190978</v>
+        <v>1.317615720554114</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.02296025223363157</v>
+        <v>0.2431329006414689</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.010016397270786</v>
+        <v>3.142119986315489</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729142822900692</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.989728453122251</v>
+        <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.418312607526511</v>
+        <v>-4.198139959118672</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.222046985797899</v>
+        <v>1.316700239342803</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.02049054577182541</v>
+        <v>0.2406631941796628</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.002022780585347</v>
+        <v>3.140710563811817</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743216620473599</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.000735375596953</v>
+        <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.486682793850521</v>
+        <v>-4.266510145442682</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.205705833742997</v>
+        <v>1.300359087287901</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.2499388932158777</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.018595122481778</v>
+        <v>3.157282905708248</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714175563978368</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.991172084228845</v>
+        <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.365266364224045</v>
+        <v>-4.145093715816206</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.244709114225479</v>
+        <v>1.339362367770383</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.2499388932158777</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.009031831113669</v>
+        <v>3.14771961434014</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710903155887702</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.815881649269231</v>
+        <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.39625952355275</v>
+        <v>-4.176086875144911</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.057021415534384</v>
+        <v>1.151674669079288</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.2499388932158777</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.833741396154056</v>
+        <v>2.972429179380526</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.7460389506759</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.820448881261019</v>
+        <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.220785263760281</v>
+        <v>-4.000612615352441</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.13177835144316</v>
+        <v>1.226431604988063</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.2499388932158777</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.838308628145843</v>
+        <v>2.976996411372314</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765020747695445</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.796190910022226</v>
+        <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.331721516401529</v>
+        <v>-4.11154886799369</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.063145879147867</v>
+        <v>1.157799132692771</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.02976624480804035</v>
+        <v>0.2499388932158777</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.81405065690705</v>
+        <v>2.952738440133521</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.77320672158129</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.799322295242132</v>
+        <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.534748093944763</v>
+        <v>-4.314575445536923</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9850666333504794</v>
+        <v>1.079719886895383</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.173260332735193</v>
+        <v>0.04691231567264431</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.695366095601016</v>
+        <v>2.834053878827487</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734159</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.809494681674264</v>
+        <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.37682249500947</v>
+        <v>-4.15664984660163</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.058409259356729</v>
+        <v>1.153062512901633</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.173260332735193</v>
+        <v>0.04691231567264431</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.705538482033149</v>
+        <v>2.844226265259619</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786946382212295</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.804440952248124</v>
+        <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.290579031983092</v>
+        <v>-4.070406383575253</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.08785291514114</v>
+        <v>1.182506168686044</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.173260332735193</v>
+        <v>0.04691231567264431</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.700484752607009</v>
+        <v>2.839172535833479</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752023923786043</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.79621672769265</v>
+        <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.291762116634153</v>
+        <v>-4.071589468226314</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.079155456725241</v>
+        <v>1.173808710270145</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1789033812017046</v>
+        <v>0.04126926720613278</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.688874698971627</v>
+        <v>2.827562482198098</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.796768600725752</v>
+        <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.16863440964007</v>
+        <v>-3.948461761232231</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.128958412555976</v>
+        <v>1.22361166610088</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1789033812017046</v>
+        <v>0.04126926720613278</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.689426572004729</v>
+        <v>2.828114355231199</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.726041292617117</v>
+        <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.075823928189211</v>
+        <v>-3.855651279781372</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.095355297027686</v>
+        <v>1.190008550572589</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.08609289975084522</v>
+        <v>0.1340797486569921</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.67438555276661</v>
+        <v>2.813073335993081</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.727914768541718</v>
+        <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.027260875968181</v>
+        <v>-3.807088227560341</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.116653993840699</v>
+        <v>1.211307247385602</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.03752984752981503</v>
+        <v>0.1826428008780223</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.705396860023829</v>
+        <v>2.8440846432503</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.722990477053441</v>
+        <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.914589657731931</v>
+        <v>-3.694417009324091</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.156798189646921</v>
+        <v>1.251451443191825</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.07514137070643517</v>
+        <v>0.2953140191142725</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.768075299477303</v>
+        <v>2.906763082703773</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.728481772884108</v>
+        <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.8887116732396</v>
+        <v>-3.677946285922073</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.172640679274521</v>
+        <v>1.2635310283833</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.07514137070643517</v>
+        <v>0.2953140191142725</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.77356659530797</v>
+        <v>2.91225437853444</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.739978974652647</v>
+        <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.086946242126331</v>
+        <v>-3.876180854808803</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.104844053488368</v>
+        <v>1.195734402597147</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1230931981802954</v>
+        <v>0.09707945022754194</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.66612305574447</v>
+        <v>2.804810838970941</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.578334694653301</v>
+        <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.16994752315161</v>
+        <v>-3.959182135834082</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9099992610789094</v>
+        <v>1.000889610187689</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1416640827074692</v>
+        <v>0.07850856570036818</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.493336245028819</v>
+        <v>2.63202402825529</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.698484355372506</v>
+        <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.010753251095034</v>
+        <v>-3.799987863777506</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.093826630620745</v>
+        <v>1.184716979729525</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1416640827074692</v>
+        <v>0.07850856570036818</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.613485905748025</v>
+        <v>2.752173688974496</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733008865660767</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.712997381474829</v>
+        <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.097351834076137</v>
+        <v>-3.886586446758609</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.073700223530627</v>
+        <v>1.164590572639407</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1416640827074692</v>
+        <v>0.07850856570036818</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.627998931850348</v>
+        <v>2.766686715076819</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.710416822817198</v>
+        <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.058968171517986</v>
+        <v>-3.848202784200458</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.086473129896256</v>
+        <v>1.177363479005036</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.103280420149318</v>
+        <v>0.1168922282585194</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.648448570727608</v>
+        <v>2.787136353954078</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751143622002483</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.7071458516625</v>
+        <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.88185184148282</v>
+        <v>-3.671086454165291</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.154048690755625</v>
+        <v>1.244939039864404</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.103280420149318</v>
+        <v>0.1168922282585194</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.64517759957291</v>
+        <v>2.78386538279938</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741324873263901</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.707829243424413</v>
+        <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.852149717506526</v>
+        <v>-3.641384330188998</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.166612932108056</v>
+        <v>1.257503281216835</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1077505453646314</v>
+        <v>0.112422103043206</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.643178916205635</v>
+        <v>2.781866699432105</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750725801481235</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.701616218730828</v>
+        <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.672774296267758</v>
+        <v>-3.46200890895023</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.232150075909977</v>
+        <v>1.323040425018756</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.04902621280608732</v>
+        <v>0.2691988612139247</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.73103194641448</v>
+        <v>2.86971972964095</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.71698814345223</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.682423674062417</v>
+        <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.717788509788365</v>
+        <v>-3.507023122470836</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.194951845833324</v>
+        <v>1.285842194942104</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.01867731749148271</v>
+        <v>0.2388499658993201</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.693630064557307</v>
+        <v>2.832317847783778</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.688115236401363</v>
+        <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.9847930200608</v>
+        <v>-3.774027632743271</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.093841604063296</v>
+        <v>1.184731953172075</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1756857205514659</v>
+        <v>0.04448692785637148</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.582703804070484</v>
+        <v>2.721391587296954</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702305879230806</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.687319158297865</v>
+        <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.273580240519715</v>
+        <v>-4.062814853202187</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9775306377762312</v>
+        <v>1.06842098688501</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2767718406504662</v>
+        <v>-0.05659919224262888</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.521256053907585</v>
+        <v>2.659943837134055</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705568086285452</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.684919119852181</v>
+        <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.241104654348943</v>
+        <v>-4.030339267031414</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.988120833798857</v>
+        <v>1.079011182907636</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2767718406504662</v>
+        <v>-0.05659919224262888</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.518856015461902</v>
+        <v>2.657543798688372</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.7095068678481</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.681443839060426</v>
+        <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.222066526641646</v>
+        <v>-4.011301139324117</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9922608040900207</v>
+        <v>1.0831511531988</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3349554519816608</v>
+        <v>-0.1147828035738234</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.48047056787143</v>
+        <v>2.6191583510979</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601249</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.859025707999107</v>
+        <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.238812391898021</v>
+        <v>-4.028047004580492</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.163144326926151</v>
+        <v>1.25403467603493</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3349554519816608</v>
+        <v>-0.1147828035738234</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.658052436810111</v>
+        <v>2.796740220036581</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.415604731774791</v>
+        <v>3.863759639096878</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.85985903698524</v>
+        <v>2.763099683924018</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.1547731855133</v>
+        <v>-4.22691664720416</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.197593338466173</v>
+        <v>1.071976600728607</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4037967567645305</v>
+        <v>-0.3136524461974907</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.617580982926522</v>
+        <v>2.574908216205524</v>
       </c>
     </row>
   </sheetData>
